--- a/projects/coupang-sourcing/excel/calc_v4_template.xlsx
+++ b/projects/coupang-sourcing/excel/calc_v4_template.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소싱현황" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="가정" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세율표" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="로켓그로스요금표" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -139,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,6 +188,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -592,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AI218"/>
+  <dimension ref="B2:AL218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.1" customWidth="1" min="1" max="1"/>
@@ -630,6 +632,9 @@
     <col width="11" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -805,6 +810,21 @@
           <t>판정</t>
         </is>
       </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>판매방식</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>사이즈단계</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>권장물류비</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="n">
@@ -823,7 +843,7 @@
       </c>
       <c r="J8" s="10" t="n"/>
       <c r="K8" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L8" s="8" t="n"/>
@@ -884,6 +904,12 @@
         <f>IF(AH8="","",IF(U8&lt;=0,"역마진",IF(AH8&gt;=가정!$C$35,"GO",IF(AH8&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ8" s="7" t="n"/>
+      <c r="AK8" s="7" t="n"/>
+      <c r="AL8" s="6">
+        <f>IF(AK8="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK8,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="n">
@@ -902,7 +928,7 @@
       </c>
       <c r="J9" s="10" t="n"/>
       <c r="K9" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L9" s="8" t="n"/>
@@ -963,6 +989,12 @@
         <f>IF(AH9="","",IF(U9&lt;=0,"역마진",IF(AH9&gt;=가정!$C$35,"GO",IF(AH9&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ9" s="7" t="n"/>
+      <c r="AK9" s="7" t="n"/>
+      <c r="AL9" s="6">
+        <f>IF(AK9="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK9,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="n">
@@ -981,7 +1013,7 @@
       </c>
       <c r="J10" s="10" t="n"/>
       <c r="K10" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L10" s="8" t="n"/>
@@ -1042,6 +1074,12 @@
         <f>IF(AH10="","",IF(U10&lt;=0,"역마진",IF(AH10&gt;=가정!$C$35,"GO",IF(AH10&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ10" s="7" t="n"/>
+      <c r="AK10" s="7" t="n"/>
+      <c r="AL10" s="6">
+        <f>IF(AK10="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK10,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="n">
@@ -1060,7 +1098,7 @@
       </c>
       <c r="J11" s="10" t="n"/>
       <c r="K11" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L11" s="8" t="n"/>
@@ -1121,6 +1159,12 @@
         <f>IF(AH11="","",IF(U11&lt;=0,"역마진",IF(AH11&gt;=가정!$C$35,"GO",IF(AH11&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ11" s="7" t="n"/>
+      <c r="AK11" s="7" t="n"/>
+      <c r="AL11" s="6">
+        <f>IF(AK11="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK11,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="n">
@@ -1139,7 +1183,7 @@
       </c>
       <c r="J12" s="10" t="n"/>
       <c r="K12" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L12" s="8" t="n"/>
@@ -1200,6 +1244,12 @@
         <f>IF(AH12="","",IF(U12&lt;=0,"역마진",IF(AH12&gt;=가정!$C$35,"GO",IF(AH12&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ12" s="7" t="n"/>
+      <c r="AK12" s="7" t="n"/>
+      <c r="AL12" s="6">
+        <f>IF(AK12="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK12,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="n">
@@ -1218,7 +1268,7 @@
       </c>
       <c r="J13" s="10" t="n"/>
       <c r="K13" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L13" s="8" t="n"/>
@@ -1279,6 +1329,12 @@
         <f>IF(AH13="","",IF(U13&lt;=0,"역마진",IF(AH13&gt;=가정!$C$35,"GO",IF(AH13&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ13" s="7" t="n"/>
+      <c r="AK13" s="7" t="n"/>
+      <c r="AL13" s="6">
+        <f>IF(AK13="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK13,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="n">
@@ -1297,7 +1353,7 @@
       </c>
       <c r="J14" s="10" t="n"/>
       <c r="K14" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L14" s="8" t="n"/>
@@ -1358,6 +1414,12 @@
         <f>IF(AH14="","",IF(U14&lt;=0,"역마진",IF(AH14&gt;=가정!$C$35,"GO",IF(AH14&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ14" s="7" t="n"/>
+      <c r="AK14" s="7" t="n"/>
+      <c r="AL14" s="6">
+        <f>IF(AK14="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK14,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="n">
@@ -1376,7 +1438,7 @@
       </c>
       <c r="J15" s="10" t="n"/>
       <c r="K15" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L15" s="8" t="n"/>
@@ -1437,6 +1499,12 @@
         <f>IF(AH15="","",IF(U15&lt;=0,"역마진",IF(AH15&gt;=가정!$C$35,"GO",IF(AH15&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ15" s="7" t="n"/>
+      <c r="AK15" s="7" t="n"/>
+      <c r="AL15" s="6">
+        <f>IF(AK15="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK15,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="n">
@@ -1455,7 +1523,7 @@
       </c>
       <c r="J16" s="10" t="n"/>
       <c r="K16" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L16" s="8" t="n"/>
@@ -1516,6 +1584,12 @@
         <f>IF(AH16="","",IF(U16&lt;=0,"역마진",IF(AH16&gt;=가정!$C$35,"GO",IF(AH16&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ16" s="7" t="n"/>
+      <c r="AK16" s="7" t="n"/>
+      <c r="AL16" s="6">
+        <f>IF(AK16="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK16,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="n">
@@ -1534,7 +1608,7 @@
       </c>
       <c r="J17" s="10" t="n"/>
       <c r="K17" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L17" s="8" t="n"/>
@@ -1595,6 +1669,12 @@
         <f>IF(AH17="","",IF(U17&lt;=0,"역마진",IF(AH17&gt;=가정!$C$35,"GO",IF(AH17&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ17" s="7" t="n"/>
+      <c r="AK17" s="7" t="n"/>
+      <c r="AL17" s="6">
+        <f>IF(AK17="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK17,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="n">
@@ -1613,7 +1693,7 @@
       </c>
       <c r="J18" s="10" t="n"/>
       <c r="K18" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L18" s="8" t="n"/>
@@ -1674,6 +1754,12 @@
         <f>IF(AH18="","",IF(U18&lt;=0,"역마진",IF(AH18&gt;=가정!$C$35,"GO",IF(AH18&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ18" s="7" t="n"/>
+      <c r="AK18" s="7" t="n"/>
+      <c r="AL18" s="6">
+        <f>IF(AK18="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK18,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="n">
@@ -1692,7 +1778,7 @@
       </c>
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L19" s="8" t="n"/>
@@ -1753,6 +1839,12 @@
         <f>IF(AH19="","",IF(U19&lt;=0,"역마진",IF(AH19&gt;=가정!$C$35,"GO",IF(AH19&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ19" s="7" t="n"/>
+      <c r="AK19" s="7" t="n"/>
+      <c r="AL19" s="6">
+        <f>IF(AK19="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK19,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="n">
@@ -1771,7 +1863,7 @@
       </c>
       <c r="J20" s="10" t="n"/>
       <c r="K20" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L20" s="8" t="n"/>
@@ -1832,6 +1924,12 @@
         <f>IF(AH20="","",IF(U20&lt;=0,"역마진",IF(AH20&gt;=가정!$C$35,"GO",IF(AH20&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ20" s="7" t="n"/>
+      <c r="AK20" s="7" t="n"/>
+      <c r="AL20" s="6">
+        <f>IF(AK20="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK20,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="n">
@@ -1850,7 +1948,7 @@
       </c>
       <c r="J21" s="10" t="n"/>
       <c r="K21" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L21" s="8" t="n"/>
@@ -1911,6 +2009,12 @@
         <f>IF(AH21="","",IF(U21&lt;=0,"역마진",IF(AH21&gt;=가정!$C$35,"GO",IF(AH21&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ21" s="7" t="n"/>
+      <c r="AK21" s="7" t="n"/>
+      <c r="AL21" s="6">
+        <f>IF(AK21="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK21,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="n">
@@ -1929,7 +2033,7 @@
       </c>
       <c r="J22" s="10" t="n"/>
       <c r="K22" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L22" s="8" t="n"/>
@@ -1990,6 +2094,12 @@
         <f>IF(AH22="","",IF(U22&lt;=0,"역마진",IF(AH22&gt;=가정!$C$35,"GO",IF(AH22&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ22" s="7" t="n"/>
+      <c r="AK22" s="7" t="n"/>
+      <c r="AL22" s="6">
+        <f>IF(AK22="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK22,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="n">
@@ -2008,7 +2118,7 @@
       </c>
       <c r="J23" s="10" t="n"/>
       <c r="K23" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L23" s="8" t="n"/>
@@ -2069,6 +2179,12 @@
         <f>IF(AH23="","",IF(U23&lt;=0,"역마진",IF(AH23&gt;=가정!$C$35,"GO",IF(AH23&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ23" s="7" t="n"/>
+      <c r="AK23" s="7" t="n"/>
+      <c r="AL23" s="6">
+        <f>IF(AK23="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK23,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="n">
@@ -2087,7 +2203,7 @@
       </c>
       <c r="J24" s="10" t="n"/>
       <c r="K24" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L24" s="8" t="n"/>
@@ -2148,6 +2264,12 @@
         <f>IF(AH24="","",IF(U24&lt;=0,"역마진",IF(AH24&gt;=가정!$C$35,"GO",IF(AH24&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ24" s="7" t="n"/>
+      <c r="AK24" s="7" t="n"/>
+      <c r="AL24" s="6">
+        <f>IF(AK24="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK24,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="n">
@@ -2166,7 +2288,7 @@
       </c>
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L25" s="8" t="n"/>
@@ -2227,6 +2349,12 @@
         <f>IF(AH25="","",IF(U25&lt;=0,"역마진",IF(AH25&gt;=가정!$C$35,"GO",IF(AH25&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ25" s="7" t="n"/>
+      <c r="AK25" s="7" t="n"/>
+      <c r="AL25" s="6">
+        <f>IF(AK25="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK25,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="n">
@@ -2245,7 +2373,7 @@
       </c>
       <c r="J26" s="10" t="n"/>
       <c r="K26" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L26" s="8" t="n"/>
@@ -2306,6 +2434,12 @@
         <f>IF(AH26="","",IF(U26&lt;=0,"역마진",IF(AH26&gt;=가정!$C$35,"GO",IF(AH26&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ26" s="7" t="n"/>
+      <c r="AK26" s="7" t="n"/>
+      <c r="AL26" s="6">
+        <f>IF(AK26="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK26,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="n">
@@ -2324,7 +2458,7 @@
       </c>
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L27" s="8" t="n"/>
@@ -2385,6 +2519,12 @@
         <f>IF(AH27="","",IF(U27&lt;=0,"역마진",IF(AH27&gt;=가정!$C$35,"GO",IF(AH27&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ27" s="7" t="n"/>
+      <c r="AK27" s="7" t="n"/>
+      <c r="AL27" s="6">
+        <f>IF(AK27="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK27,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="n">
@@ -2403,7 +2543,7 @@
       </c>
       <c r="J28" s="10" t="n"/>
       <c r="K28" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L28" s="8" t="n"/>
@@ -2464,6 +2604,12 @@
         <f>IF(AH28="","",IF(U28&lt;=0,"역마진",IF(AH28&gt;=가정!$C$35,"GO",IF(AH28&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ28" s="7" t="n"/>
+      <c r="AK28" s="7" t="n"/>
+      <c r="AL28" s="6">
+        <f>IF(AK28="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK28,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="n">
@@ -2482,7 +2628,7 @@
       </c>
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L29" s="8" t="n"/>
@@ -2543,6 +2689,12 @@
         <f>IF(AH29="","",IF(U29&lt;=0,"역마진",IF(AH29&gt;=가정!$C$35,"GO",IF(AH29&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ29" s="7" t="n"/>
+      <c r="AK29" s="7" t="n"/>
+      <c r="AL29" s="6">
+        <f>IF(AK29="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK29,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="n">
@@ -2561,7 +2713,7 @@
       </c>
       <c r="J30" s="10" t="n"/>
       <c r="K30" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L30" s="8" t="n"/>
@@ -2622,6 +2774,12 @@
         <f>IF(AH30="","",IF(U30&lt;=0,"역마진",IF(AH30&gt;=가정!$C$35,"GO",IF(AH30&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ30" s="7" t="n"/>
+      <c r="AK30" s="7" t="n"/>
+      <c r="AL30" s="6">
+        <f>IF(AK30="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK30,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="n">
@@ -2640,7 +2798,7 @@
       </c>
       <c r="J31" s="10" t="n"/>
       <c r="K31" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L31" s="8" t="n"/>
@@ -2701,6 +2859,12 @@
         <f>IF(AH31="","",IF(U31&lt;=0,"역마진",IF(AH31&gt;=가정!$C$35,"GO",IF(AH31&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ31" s="7" t="n"/>
+      <c r="AK31" s="7" t="n"/>
+      <c r="AL31" s="6">
+        <f>IF(AK31="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK31,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="n">
@@ -2719,7 +2883,7 @@
       </c>
       <c r="J32" s="10" t="n"/>
       <c r="K32" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L32" s="8" t="n"/>
@@ -2780,6 +2944,12 @@
         <f>IF(AH32="","",IF(U32&lt;=0,"역마진",IF(AH32&gt;=가정!$C$35,"GO",IF(AH32&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ32" s="7" t="n"/>
+      <c r="AK32" s="7" t="n"/>
+      <c r="AL32" s="6">
+        <f>IF(AK32="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK32,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="n">
@@ -2798,7 +2968,7 @@
       </c>
       <c r="J33" s="10" t="n"/>
       <c r="K33" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L33" s="8" t="n"/>
@@ -2859,6 +3029,12 @@
         <f>IF(AH33="","",IF(U33&lt;=0,"역마진",IF(AH33&gt;=가정!$C$35,"GO",IF(AH33&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ33" s="7" t="n"/>
+      <c r="AK33" s="7" t="n"/>
+      <c r="AL33" s="6">
+        <f>IF(AK33="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK33,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="n">
@@ -2877,7 +3053,7 @@
       </c>
       <c r="J34" s="10" t="n"/>
       <c r="K34" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L34" s="8" t="n"/>
@@ -2938,6 +3114,12 @@
         <f>IF(AH34="","",IF(U34&lt;=0,"역마진",IF(AH34&gt;=가정!$C$35,"GO",IF(AH34&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ34" s="7" t="n"/>
+      <c r="AK34" s="7" t="n"/>
+      <c r="AL34" s="6">
+        <f>IF(AK34="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK34,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="n">
@@ -2956,7 +3138,7 @@
       </c>
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L35" s="8" t="n"/>
@@ -3017,6 +3199,12 @@
         <f>IF(AH35="","",IF(U35&lt;=0,"역마진",IF(AH35&gt;=가정!$C$35,"GO",IF(AH35&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ35" s="7" t="n"/>
+      <c r="AK35" s="7" t="n"/>
+      <c r="AL35" s="6">
+        <f>IF(AK35="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK35,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="n">
@@ -3035,7 +3223,7 @@
       </c>
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L36" s="8" t="n"/>
@@ -3096,6 +3284,12 @@
         <f>IF(AH36="","",IF(U36&lt;=0,"역마진",IF(AH36&gt;=가정!$C$35,"GO",IF(AH36&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ36" s="7" t="n"/>
+      <c r="AK36" s="7" t="n"/>
+      <c r="AL36" s="6">
+        <f>IF(AK36="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK36,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="n">
@@ -3114,7 +3308,7 @@
       </c>
       <c r="J37" s="10" t="n"/>
       <c r="K37" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L37" s="8" t="n"/>
@@ -3175,6 +3369,12 @@
         <f>IF(AH37="","",IF(U37&lt;=0,"역마진",IF(AH37&gt;=가정!$C$35,"GO",IF(AH37&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ37" s="7" t="n"/>
+      <c r="AK37" s="7" t="n"/>
+      <c r="AL37" s="6">
+        <f>IF(AK37="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK37,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="n">
@@ -3193,7 +3393,7 @@
       </c>
       <c r="J38" s="10" t="n"/>
       <c r="K38" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L38" s="8" t="n"/>
@@ -3254,6 +3454,12 @@
         <f>IF(AH38="","",IF(U38&lt;=0,"역마진",IF(AH38&gt;=가정!$C$35,"GO",IF(AH38&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ38" s="7" t="n"/>
+      <c r="AK38" s="7" t="n"/>
+      <c r="AL38" s="6">
+        <f>IF(AK38="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK38,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="n">
@@ -3272,7 +3478,7 @@
       </c>
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L39" s="8" t="n"/>
@@ -3333,6 +3539,12 @@
         <f>IF(AH39="","",IF(U39&lt;=0,"역마진",IF(AH39&gt;=가정!$C$35,"GO",IF(AH39&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ39" s="7" t="n"/>
+      <c r="AK39" s="7" t="n"/>
+      <c r="AL39" s="6">
+        <f>IF(AK39="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK39,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="n">
@@ -3351,7 +3563,7 @@
       </c>
       <c r="J40" s="10" t="n"/>
       <c r="K40" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L40" s="8" t="n"/>
@@ -3412,6 +3624,12 @@
         <f>IF(AH40="","",IF(U40&lt;=0,"역마진",IF(AH40&gt;=가정!$C$35,"GO",IF(AH40&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ40" s="7" t="n"/>
+      <c r="AK40" s="7" t="n"/>
+      <c r="AL40" s="6">
+        <f>IF(AK40="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK40,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="6" t="n">
@@ -3430,7 +3648,7 @@
       </c>
       <c r="J41" s="10" t="n"/>
       <c r="K41" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L41" s="8" t="n"/>
@@ -3491,6 +3709,12 @@
         <f>IF(AH41="","",IF(U41&lt;=0,"역마진",IF(AH41&gt;=가정!$C$35,"GO",IF(AH41&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ41" s="7" t="n"/>
+      <c r="AK41" s="7" t="n"/>
+      <c r="AL41" s="6">
+        <f>IF(AK41="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK41,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="n">
@@ -3509,7 +3733,7 @@
       </c>
       <c r="J42" s="10" t="n"/>
       <c r="K42" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L42" s="8" t="n"/>
@@ -3570,6 +3794,12 @@
         <f>IF(AH42="","",IF(U42&lt;=0,"역마진",IF(AH42&gt;=가정!$C$35,"GO",IF(AH42&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ42" s="7" t="n"/>
+      <c r="AK42" s="7" t="n"/>
+      <c r="AL42" s="6">
+        <f>IF(AK42="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK42,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="n">
@@ -3588,7 +3818,7 @@
       </c>
       <c r="J43" s="10" t="n"/>
       <c r="K43" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L43" s="8" t="n"/>
@@ -3649,6 +3879,12 @@
         <f>IF(AH43="","",IF(U43&lt;=0,"역마진",IF(AH43&gt;=가정!$C$35,"GO",IF(AH43&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ43" s="7" t="n"/>
+      <c r="AK43" s="7" t="n"/>
+      <c r="AL43" s="6">
+        <f>IF(AK43="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK43,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="n">
@@ -3667,7 +3903,7 @@
       </c>
       <c r="J44" s="10" t="n"/>
       <c r="K44" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L44" s="8" t="n"/>
@@ -3728,6 +3964,12 @@
         <f>IF(AH44="","",IF(U44&lt;=0,"역마진",IF(AH44&gt;=가정!$C$35,"GO",IF(AH44&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ44" s="7" t="n"/>
+      <c r="AK44" s="7" t="n"/>
+      <c r="AL44" s="6">
+        <f>IF(AK44="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK44,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="n">
@@ -3746,7 +3988,7 @@
       </c>
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L45" s="8" t="n"/>
@@ -3807,6 +4049,12 @@
         <f>IF(AH45="","",IF(U45&lt;=0,"역마진",IF(AH45&gt;=가정!$C$35,"GO",IF(AH45&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ45" s="7" t="n"/>
+      <c r="AK45" s="7" t="n"/>
+      <c r="AL45" s="6">
+        <f>IF(AK45="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK45,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="n">
@@ -3825,7 +4073,7 @@
       </c>
       <c r="J46" s="10" t="n"/>
       <c r="K46" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L46" s="8" t="n"/>
@@ -3886,6 +4134,12 @@
         <f>IF(AH46="","",IF(U46&lt;=0,"역마진",IF(AH46&gt;=가정!$C$35,"GO",IF(AH46&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ46" s="7" t="n"/>
+      <c r="AK46" s="7" t="n"/>
+      <c r="AL46" s="6">
+        <f>IF(AK46="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK46,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="n">
@@ -3904,7 +4158,7 @@
       </c>
       <c r="J47" s="10" t="n"/>
       <c r="K47" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L47" s="8" t="n"/>
@@ -3965,6 +4219,12 @@
         <f>IF(AH47="","",IF(U47&lt;=0,"역마진",IF(AH47&gt;=가정!$C$35,"GO",IF(AH47&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ47" s="7" t="n"/>
+      <c r="AK47" s="7" t="n"/>
+      <c r="AL47" s="6">
+        <f>IF(AK47="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK47,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="n">
@@ -3983,7 +4243,7 @@
       </c>
       <c r="J48" s="10" t="n"/>
       <c r="K48" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L48" s="8" t="n"/>
@@ -4044,6 +4304,12 @@
         <f>IF(AH48="","",IF(U48&lt;=0,"역마진",IF(AH48&gt;=가정!$C$35,"GO",IF(AH48&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ48" s="7" t="n"/>
+      <c r="AK48" s="7" t="n"/>
+      <c r="AL48" s="6">
+        <f>IF(AK48="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK48,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="n">
@@ -4062,7 +4328,7 @@
       </c>
       <c r="J49" s="10" t="n"/>
       <c r="K49" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L49" s="8" t="n"/>
@@ -4123,6 +4389,12 @@
         <f>IF(AH49="","",IF(U49&lt;=0,"역마진",IF(AH49&gt;=가정!$C$35,"GO",IF(AH49&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ49" s="7" t="n"/>
+      <c r="AK49" s="7" t="n"/>
+      <c r="AL49" s="6">
+        <f>IF(AK49="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK49,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="n">
@@ -4141,7 +4413,7 @@
       </c>
       <c r="J50" s="10" t="n"/>
       <c r="K50" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L50" s="8" t="n"/>
@@ -4202,6 +4474,12 @@
         <f>IF(AH50="","",IF(U50&lt;=0,"역마진",IF(AH50&gt;=가정!$C$35,"GO",IF(AH50&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ50" s="7" t="n"/>
+      <c r="AK50" s="7" t="n"/>
+      <c r="AL50" s="6">
+        <f>IF(AK50="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK50,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="6" t="n">
@@ -4220,7 +4498,7 @@
       </c>
       <c r="J51" s="10" t="n"/>
       <c r="K51" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L51" s="8" t="n"/>
@@ -4281,6 +4559,12 @@
         <f>IF(AH51="","",IF(U51&lt;=0,"역마진",IF(AH51&gt;=가정!$C$35,"GO",IF(AH51&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ51" s="7" t="n"/>
+      <c r="AK51" s="7" t="n"/>
+      <c r="AL51" s="6">
+        <f>IF(AK51="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK51,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="n">
@@ -4299,7 +4583,7 @@
       </c>
       <c r="J52" s="10" t="n"/>
       <c r="K52" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L52" s="8" t="n"/>
@@ -4360,6 +4644,12 @@
         <f>IF(AH52="","",IF(U52&lt;=0,"역마진",IF(AH52&gt;=가정!$C$35,"GO",IF(AH52&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ52" s="7" t="n"/>
+      <c r="AK52" s="7" t="n"/>
+      <c r="AL52" s="6">
+        <f>IF(AK52="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK52,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="n">
@@ -4378,7 +4668,7 @@
       </c>
       <c r="J53" s="10" t="n"/>
       <c r="K53" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L53" s="8" t="n"/>
@@ -4439,6 +4729,12 @@
         <f>IF(AH53="","",IF(U53&lt;=0,"역마진",IF(AH53&gt;=가정!$C$35,"GO",IF(AH53&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ53" s="7" t="n"/>
+      <c r="AK53" s="7" t="n"/>
+      <c r="AL53" s="6">
+        <f>IF(AK53="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK53,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="n">
@@ -4457,7 +4753,7 @@
       </c>
       <c r="J54" s="10" t="n"/>
       <c r="K54" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L54" s="8" t="n"/>
@@ -4518,6 +4814,12 @@
         <f>IF(AH54="","",IF(U54&lt;=0,"역마진",IF(AH54&gt;=가정!$C$35,"GO",IF(AH54&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ54" s="7" t="n"/>
+      <c r="AK54" s="7" t="n"/>
+      <c r="AL54" s="6">
+        <f>IF(AK54="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK54,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="n">
@@ -4536,7 +4838,7 @@
       </c>
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L55" s="8" t="n"/>
@@ -4597,6 +4899,12 @@
         <f>IF(AH55="","",IF(U55&lt;=0,"역마진",IF(AH55&gt;=가정!$C$35,"GO",IF(AH55&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ55" s="7" t="n"/>
+      <c r="AK55" s="7" t="n"/>
+      <c r="AL55" s="6">
+        <f>IF(AK55="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK55,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="n">
@@ -4615,7 +4923,7 @@
       </c>
       <c r="J56" s="10" t="n"/>
       <c r="K56" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L56" s="8" t="n"/>
@@ -4676,6 +4984,12 @@
         <f>IF(AH56="","",IF(U56&lt;=0,"역마진",IF(AH56&gt;=가정!$C$35,"GO",IF(AH56&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ56" s="7" t="n"/>
+      <c r="AK56" s="7" t="n"/>
+      <c r="AL56" s="6">
+        <f>IF(AK56="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK56,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="B57" s="6" t="n">
@@ -4694,7 +5008,7 @@
       </c>
       <c r="J57" s="10" t="n"/>
       <c r="K57" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L57" s="8" t="n"/>
@@ -4755,6 +5069,12 @@
         <f>IF(AH57="","",IF(U57&lt;=0,"역마진",IF(AH57&gt;=가정!$C$35,"GO",IF(AH57&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ57" s="7" t="n"/>
+      <c r="AK57" s="7" t="n"/>
+      <c r="AL57" s="6">
+        <f>IF(AK57="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK57,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="n">
@@ -4773,7 +5093,7 @@
       </c>
       <c r="J58" s="10" t="n"/>
       <c r="K58" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L58" s="8" t="n"/>
@@ -4834,6 +5154,12 @@
         <f>IF(AH58="","",IF(U58&lt;=0,"역마진",IF(AH58&gt;=가정!$C$35,"GO",IF(AH58&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ58" s="7" t="n"/>
+      <c r="AK58" s="7" t="n"/>
+      <c r="AL58" s="6">
+        <f>IF(AK58="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK58,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="B59" s="6" t="n">
@@ -4852,7 +5178,7 @@
       </c>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L59" s="8" t="n"/>
@@ -4913,6 +5239,12 @@
         <f>IF(AH59="","",IF(U59&lt;=0,"역마진",IF(AH59&gt;=가정!$C$35,"GO",IF(AH59&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ59" s="7" t="n"/>
+      <c r="AK59" s="7" t="n"/>
+      <c r="AL59" s="6">
+        <f>IF(AK59="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK59,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="n">
@@ -4931,7 +5263,7 @@
       </c>
       <c r="J60" s="10" t="n"/>
       <c r="K60" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L60" s="8" t="n"/>
@@ -4992,6 +5324,12 @@
         <f>IF(AH60="","",IF(U60&lt;=0,"역마진",IF(AH60&gt;=가정!$C$35,"GO",IF(AH60&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ60" s="7" t="n"/>
+      <c r="AK60" s="7" t="n"/>
+      <c r="AL60" s="6">
+        <f>IF(AK60="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK60,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="B61" s="6" t="n">
@@ -5010,7 +5348,7 @@
       </c>
       <c r="J61" s="10" t="n"/>
       <c r="K61" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L61" s="8" t="n"/>
@@ -5071,6 +5409,12 @@
         <f>IF(AH61="","",IF(U61&lt;=0,"역마진",IF(AH61&gt;=가정!$C$35,"GO",IF(AH61&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ61" s="7" t="n"/>
+      <c r="AK61" s="7" t="n"/>
+      <c r="AL61" s="6">
+        <f>IF(AK61="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK61,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="n">
@@ -5089,7 +5433,7 @@
       </c>
       <c r="J62" s="10" t="n"/>
       <c r="K62" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L62" s="8" t="n"/>
@@ -5150,6 +5494,12 @@
         <f>IF(AH62="","",IF(U62&lt;=0,"역마진",IF(AH62&gt;=가정!$C$35,"GO",IF(AH62&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ62" s="7" t="n"/>
+      <c r="AK62" s="7" t="n"/>
+      <c r="AL62" s="6">
+        <f>IF(AK62="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK62,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="6" t="n">
@@ -5168,7 +5518,7 @@
       </c>
       <c r="J63" s="10" t="n"/>
       <c r="K63" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L63" s="8" t="n"/>
@@ -5229,6 +5579,12 @@
         <f>IF(AH63="","",IF(U63&lt;=0,"역마진",IF(AH63&gt;=가정!$C$35,"GO",IF(AH63&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ63" s="7" t="n"/>
+      <c r="AK63" s="7" t="n"/>
+      <c r="AL63" s="6">
+        <f>IF(AK63="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK63,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="n">
@@ -5247,7 +5603,7 @@
       </c>
       <c r="J64" s="10" t="n"/>
       <c r="K64" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L64" s="8" t="n"/>
@@ -5308,6 +5664,12 @@
         <f>IF(AH64="","",IF(U64&lt;=0,"역마진",IF(AH64&gt;=가정!$C$35,"GO",IF(AH64&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ64" s="7" t="n"/>
+      <c r="AK64" s="7" t="n"/>
+      <c r="AL64" s="6">
+        <f>IF(AK64="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK64,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="6" t="n">
@@ -5326,7 +5688,7 @@
       </c>
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L65" s="8" t="n"/>
@@ -5387,6 +5749,12 @@
         <f>IF(AH65="","",IF(U65&lt;=0,"역마진",IF(AH65&gt;=가정!$C$35,"GO",IF(AH65&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ65" s="7" t="n"/>
+      <c r="AK65" s="7" t="n"/>
+      <c r="AL65" s="6">
+        <f>IF(AK65="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK65,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="n">
@@ -5405,7 +5773,7 @@
       </c>
       <c r="J66" s="10" t="n"/>
       <c r="K66" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L66" s="8" t="n"/>
@@ -5466,6 +5834,12 @@
         <f>IF(AH66="","",IF(U66&lt;=0,"역마진",IF(AH66&gt;=가정!$C$35,"GO",IF(AH66&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ66" s="7" t="n"/>
+      <c r="AK66" s="7" t="n"/>
+      <c r="AL66" s="6">
+        <f>IF(AK66="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK66,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="6" t="n">
@@ -5484,7 +5858,7 @@
       </c>
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L67" s="8" t="n"/>
@@ -5545,6 +5919,12 @@
         <f>IF(AH67="","",IF(U67&lt;=0,"역마진",IF(AH67&gt;=가정!$C$35,"GO",IF(AH67&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ67" s="7" t="n"/>
+      <c r="AK67" s="7" t="n"/>
+      <c r="AL67" s="6">
+        <f>IF(AK67="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK67,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="n">
@@ -5563,7 +5943,7 @@
       </c>
       <c r="J68" s="10" t="n"/>
       <c r="K68" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L68" s="8" t="n"/>
@@ -5624,6 +6004,12 @@
         <f>IF(AH68="","",IF(U68&lt;=0,"역마진",IF(AH68&gt;=가정!$C$35,"GO",IF(AH68&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ68" s="7" t="n"/>
+      <c r="AK68" s="7" t="n"/>
+      <c r="AL68" s="6">
+        <f>IF(AK68="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK68,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="B69" s="6" t="n">
@@ -5642,7 +6028,7 @@
       </c>
       <c r="J69" s="10" t="n"/>
       <c r="K69" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L69" s="8" t="n"/>
@@ -5703,6 +6089,12 @@
         <f>IF(AH69="","",IF(U69&lt;=0,"역마진",IF(AH69&gt;=가정!$C$35,"GO",IF(AH69&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ69" s="7" t="n"/>
+      <c r="AK69" s="7" t="n"/>
+      <c r="AL69" s="6">
+        <f>IF(AK69="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK69,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="n">
@@ -5721,7 +6113,7 @@
       </c>
       <c r="J70" s="10" t="n"/>
       <c r="K70" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L70" s="8" t="n"/>
@@ -5782,6 +6174,12 @@
         <f>IF(AH70="","",IF(U70&lt;=0,"역마진",IF(AH70&gt;=가정!$C$35,"GO",IF(AH70&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ70" s="7" t="n"/>
+      <c r="AK70" s="7" t="n"/>
+      <c r="AL70" s="6">
+        <f>IF(AK70="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK70,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="B71" s="6" t="n">
@@ -5800,7 +6198,7 @@
       </c>
       <c r="J71" s="10" t="n"/>
       <c r="K71" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L71" s="8" t="n"/>
@@ -5861,6 +6259,12 @@
         <f>IF(AH71="","",IF(U71&lt;=0,"역마진",IF(AH71&gt;=가정!$C$35,"GO",IF(AH71&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ71" s="7" t="n"/>
+      <c r="AK71" s="7" t="n"/>
+      <c r="AL71" s="6">
+        <f>IF(AK71="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK71,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="n">
@@ -5879,7 +6283,7 @@
       </c>
       <c r="J72" s="10" t="n"/>
       <c r="K72" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L72" s="8" t="n"/>
@@ -5940,6 +6344,12 @@
         <f>IF(AH72="","",IF(U72&lt;=0,"역마진",IF(AH72&gt;=가정!$C$35,"GO",IF(AH72&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ72" s="7" t="n"/>
+      <c r="AK72" s="7" t="n"/>
+      <c r="AL72" s="6">
+        <f>IF(AK72="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK72,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="B73" s="6" t="n">
@@ -5958,7 +6368,7 @@
       </c>
       <c r="J73" s="10" t="n"/>
       <c r="K73" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L73" s="8" t="n"/>
@@ -6019,6 +6429,12 @@
         <f>IF(AH73="","",IF(U73&lt;=0,"역마진",IF(AH73&gt;=가정!$C$35,"GO",IF(AH73&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ73" s="7" t="n"/>
+      <c r="AK73" s="7" t="n"/>
+      <c r="AL73" s="6">
+        <f>IF(AK73="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK73,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="6" t="n">
@@ -6037,7 +6453,7 @@
       </c>
       <c r="J74" s="10" t="n"/>
       <c r="K74" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L74" s="8" t="n"/>
@@ -6098,6 +6514,12 @@
         <f>IF(AH74="","",IF(U74&lt;=0,"역마진",IF(AH74&gt;=가정!$C$35,"GO",IF(AH74&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ74" s="7" t="n"/>
+      <c r="AK74" s="7" t="n"/>
+      <c r="AL74" s="6">
+        <f>IF(AK74="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK74,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="B75" s="6" t="n">
@@ -6116,7 +6538,7 @@
       </c>
       <c r="J75" s="10" t="n"/>
       <c r="K75" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L75" s="8" t="n"/>
@@ -6177,6 +6599,12 @@
         <f>IF(AH75="","",IF(U75&lt;=0,"역마진",IF(AH75&gt;=가정!$C$35,"GO",IF(AH75&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ75" s="7" t="n"/>
+      <c r="AK75" s="7" t="n"/>
+      <c r="AL75" s="6">
+        <f>IF(AK75="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK75,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="B76" s="6" t="n">
@@ -6195,7 +6623,7 @@
       </c>
       <c r="J76" s="10" t="n"/>
       <c r="K76" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L76" s="8" t="n"/>
@@ -6256,6 +6684,12 @@
         <f>IF(AH76="","",IF(U76&lt;=0,"역마진",IF(AH76&gt;=가정!$C$35,"GO",IF(AH76&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ76" s="7" t="n"/>
+      <c r="AK76" s="7" t="n"/>
+      <c r="AL76" s="6">
+        <f>IF(AK76="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK76,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="6" t="n">
@@ -6274,7 +6708,7 @@
       </c>
       <c r="J77" s="10" t="n"/>
       <c r="K77" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L77" s="8" t="n"/>
@@ -6335,6 +6769,12 @@
         <f>IF(AH77="","",IF(U77&lt;=0,"역마진",IF(AH77&gt;=가정!$C$35,"GO",IF(AH77&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ77" s="7" t="n"/>
+      <c r="AK77" s="7" t="n"/>
+      <c r="AL77" s="6">
+        <f>IF(AK77="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK77,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="6" t="n">
@@ -6353,7 +6793,7 @@
       </c>
       <c r="J78" s="10" t="n"/>
       <c r="K78" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L78" s="8" t="n"/>
@@ -6414,6 +6854,12 @@
         <f>IF(AH78="","",IF(U78&lt;=0,"역마진",IF(AH78&gt;=가정!$C$35,"GO",IF(AH78&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ78" s="7" t="n"/>
+      <c r="AK78" s="7" t="n"/>
+      <c r="AL78" s="6">
+        <f>IF(AK78="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK78,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="6" t="n">
@@ -6432,7 +6878,7 @@
       </c>
       <c r="J79" s="10" t="n"/>
       <c r="K79" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L79" s="8" t="n"/>
@@ -6493,6 +6939,12 @@
         <f>IF(AH79="","",IF(U79&lt;=0,"역마진",IF(AH79&gt;=가정!$C$35,"GO",IF(AH79&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ79" s="7" t="n"/>
+      <c r="AK79" s="7" t="n"/>
+      <c r="AL79" s="6">
+        <f>IF(AK79="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK79,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="B80" s="6" t="n">
@@ -6511,7 +6963,7 @@
       </c>
       <c r="J80" s="10" t="n"/>
       <c r="K80" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L80" s="8" t="n"/>
@@ -6572,6 +7024,12 @@
         <f>IF(AH80="","",IF(U80&lt;=0,"역마진",IF(AH80&gt;=가정!$C$35,"GO",IF(AH80&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ80" s="7" t="n"/>
+      <c r="AK80" s="7" t="n"/>
+      <c r="AL80" s="6">
+        <f>IF(AK80="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK80,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="6" t="n">
@@ -6590,7 +7048,7 @@
       </c>
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L81" s="8" t="n"/>
@@ -6651,6 +7109,12 @@
         <f>IF(AH81="","",IF(U81&lt;=0,"역마진",IF(AH81&gt;=가정!$C$35,"GO",IF(AH81&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ81" s="7" t="n"/>
+      <c r="AK81" s="7" t="n"/>
+      <c r="AL81" s="6">
+        <f>IF(AK81="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK81,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="n">
@@ -6669,7 +7133,7 @@
       </c>
       <c r="J82" s="10" t="n"/>
       <c r="K82" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L82" s="8" t="n"/>
@@ -6730,6 +7194,12 @@
         <f>IF(AH82="","",IF(U82&lt;=0,"역마진",IF(AH82&gt;=가정!$C$35,"GO",IF(AH82&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ82" s="7" t="n"/>
+      <c r="AK82" s="7" t="n"/>
+      <c r="AL82" s="6">
+        <f>IF(AK82="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK82,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="n">
@@ -6748,7 +7218,7 @@
       </c>
       <c r="J83" s="10" t="n"/>
       <c r="K83" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L83" s="8" t="n"/>
@@ -6809,6 +7279,12 @@
         <f>IF(AH83="","",IF(U83&lt;=0,"역마진",IF(AH83&gt;=가정!$C$35,"GO",IF(AH83&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ83" s="7" t="n"/>
+      <c r="AK83" s="7" t="n"/>
+      <c r="AL83" s="6">
+        <f>IF(AK83="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK83,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="n">
@@ -6827,7 +7303,7 @@
       </c>
       <c r="J84" s="10" t="n"/>
       <c r="K84" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L84" s="8" t="n"/>
@@ -6888,6 +7364,12 @@
         <f>IF(AH84="","",IF(U84&lt;=0,"역마진",IF(AH84&gt;=가정!$C$35,"GO",IF(AH84&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ84" s="7" t="n"/>
+      <c r="AK84" s="7" t="n"/>
+      <c r="AL84" s="6">
+        <f>IF(AK84="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK84,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="n">
@@ -6906,7 +7388,7 @@
       </c>
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L85" s="8" t="n"/>
@@ -6967,6 +7449,12 @@
         <f>IF(AH85="","",IF(U85&lt;=0,"역마진",IF(AH85&gt;=가정!$C$35,"GO",IF(AH85&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ85" s="7" t="n"/>
+      <c r="AK85" s="7" t="n"/>
+      <c r="AL85" s="6">
+        <f>IF(AK85="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK85,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="n">
@@ -6985,7 +7473,7 @@
       </c>
       <c r="J86" s="10" t="n"/>
       <c r="K86" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L86" s="8" t="n"/>
@@ -7046,6 +7534,12 @@
         <f>IF(AH86="","",IF(U86&lt;=0,"역마진",IF(AH86&gt;=가정!$C$35,"GO",IF(AH86&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ86" s="7" t="n"/>
+      <c r="AK86" s="7" t="n"/>
+      <c r="AL86" s="6">
+        <f>IF(AK86="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK86,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="6" t="n">
@@ -7064,7 +7558,7 @@
       </c>
       <c r="J87" s="10" t="n"/>
       <c r="K87" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L87" s="8" t="n"/>
@@ -7125,6 +7619,12 @@
         <f>IF(AH87="","",IF(U87&lt;=0,"역마진",IF(AH87&gt;=가정!$C$35,"GO",IF(AH87&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ87" s="7" t="n"/>
+      <c r="AK87" s="7" t="n"/>
+      <c r="AL87" s="6">
+        <f>IF(AK87="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK87,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="6" t="n">
@@ -7143,7 +7643,7 @@
       </c>
       <c r="J88" s="10" t="n"/>
       <c r="K88" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L88" s="8" t="n"/>
@@ -7204,6 +7704,12 @@
         <f>IF(AH88="","",IF(U88&lt;=0,"역마진",IF(AH88&gt;=가정!$C$35,"GO",IF(AH88&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ88" s="7" t="n"/>
+      <c r="AK88" s="7" t="n"/>
+      <c r="AL88" s="6">
+        <f>IF(AK88="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK88,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="6" t="n">
@@ -7222,7 +7728,7 @@
       </c>
       <c r="J89" s="10" t="n"/>
       <c r="K89" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L89" s="8" t="n"/>
@@ -7283,6 +7789,12 @@
         <f>IF(AH89="","",IF(U89&lt;=0,"역마진",IF(AH89&gt;=가정!$C$35,"GO",IF(AH89&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ89" s="7" t="n"/>
+      <c r="AK89" s="7" t="n"/>
+      <c r="AL89" s="6">
+        <f>IF(AK89="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK89,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="B90" s="6" t="n">
@@ -7301,7 +7813,7 @@
       </c>
       <c r="J90" s="10" t="n"/>
       <c r="K90" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L90" s="8" t="n"/>
@@ -7362,6 +7874,12 @@
         <f>IF(AH90="","",IF(U90&lt;=0,"역마진",IF(AH90&gt;=가정!$C$35,"GO",IF(AH90&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ90" s="7" t="n"/>
+      <c r="AK90" s="7" t="n"/>
+      <c r="AL90" s="6">
+        <f>IF(AK90="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK90,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="B91" s="6" t="n">
@@ -7380,7 +7898,7 @@
       </c>
       <c r="J91" s="10" t="n"/>
       <c r="K91" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L91" s="8" t="n"/>
@@ -7441,6 +7959,12 @@
         <f>IF(AH91="","",IF(U91&lt;=0,"역마진",IF(AH91&gt;=가정!$C$35,"GO",IF(AH91&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ91" s="7" t="n"/>
+      <c r="AK91" s="7" t="n"/>
+      <c r="AL91" s="6">
+        <f>IF(AK91="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK91,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="6" t="n">
@@ -7459,7 +7983,7 @@
       </c>
       <c r="J92" s="10" t="n"/>
       <c r="K92" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L92" s="8" t="n"/>
@@ -7520,6 +8044,12 @@
         <f>IF(AH92="","",IF(U92&lt;=0,"역마진",IF(AH92&gt;=가정!$C$35,"GO",IF(AH92&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ92" s="7" t="n"/>
+      <c r="AK92" s="7" t="n"/>
+      <c r="AL92" s="6">
+        <f>IF(AK92="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK92,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="B93" s="6" t="n">
@@ -7538,7 +8068,7 @@
       </c>
       <c r="J93" s="10" t="n"/>
       <c r="K93" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L93" s="8" t="n"/>
@@ -7599,6 +8129,12 @@
         <f>IF(AH93="","",IF(U93&lt;=0,"역마진",IF(AH93&gt;=가정!$C$35,"GO",IF(AH93&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ93" s="7" t="n"/>
+      <c r="AK93" s="7" t="n"/>
+      <c r="AL93" s="6">
+        <f>IF(AK93="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK93,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="n">
@@ -7617,7 +8153,7 @@
       </c>
       <c r="J94" s="10" t="n"/>
       <c r="K94" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L94" s="8" t="n"/>
@@ -7678,6 +8214,12 @@
         <f>IF(AH94="","",IF(U94&lt;=0,"역마진",IF(AH94&gt;=가정!$C$35,"GO",IF(AH94&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ94" s="7" t="n"/>
+      <c r="AK94" s="7" t="n"/>
+      <c r="AL94" s="6">
+        <f>IF(AK94="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK94,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="B95" s="6" t="n">
@@ -7696,7 +8238,7 @@
       </c>
       <c r="J95" s="10" t="n"/>
       <c r="K95" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L95" s="8" t="n"/>
@@ -7757,6 +8299,12 @@
         <f>IF(AH95="","",IF(U95&lt;=0,"역마진",IF(AH95&gt;=가정!$C$35,"GO",IF(AH95&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ95" s="7" t="n"/>
+      <c r="AK95" s="7" t="n"/>
+      <c r="AL95" s="6">
+        <f>IF(AK95="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK95,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="B96" s="6" t="n">
@@ -7775,7 +8323,7 @@
       </c>
       <c r="J96" s="10" t="n"/>
       <c r="K96" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L96" s="8" t="n"/>
@@ -7836,6 +8384,12 @@
         <f>IF(AH96="","",IF(U96&lt;=0,"역마진",IF(AH96&gt;=가정!$C$35,"GO",IF(AH96&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ96" s="7" t="n"/>
+      <c r="AK96" s="7" t="n"/>
+      <c r="AL96" s="6">
+        <f>IF(AK96="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK96,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="B97" s="6" t="n">
@@ -7854,7 +8408,7 @@
       </c>
       <c r="J97" s="10" t="n"/>
       <c r="K97" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L97" s="8" t="n"/>
@@ -7915,6 +8469,12 @@
         <f>IF(AH97="","",IF(U97&lt;=0,"역마진",IF(AH97&gt;=가정!$C$35,"GO",IF(AH97&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ97" s="7" t="n"/>
+      <c r="AK97" s="7" t="n"/>
+      <c r="AL97" s="6">
+        <f>IF(AK97="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK97,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="n">
@@ -7933,7 +8493,7 @@
       </c>
       <c r="J98" s="10" t="n"/>
       <c r="K98" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L98" s="8" t="n"/>
@@ -7994,6 +8554,12 @@
         <f>IF(AH98="","",IF(U98&lt;=0,"역마진",IF(AH98&gt;=가정!$C$35,"GO",IF(AH98&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ98" s="7" t="n"/>
+      <c r="AK98" s="7" t="n"/>
+      <c r="AL98" s="6">
+        <f>IF(AK98="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK98,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="B99" s="6" t="n">
@@ -8012,7 +8578,7 @@
       </c>
       <c r="J99" s="10" t="n"/>
       <c r="K99" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L99" s="8" t="n"/>
@@ -8073,6 +8639,12 @@
         <f>IF(AH99="","",IF(U99&lt;=0,"역마진",IF(AH99&gt;=가정!$C$35,"GO",IF(AH99&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ99" s="7" t="n"/>
+      <c r="AK99" s="7" t="n"/>
+      <c r="AL99" s="6">
+        <f>IF(AK99="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK99,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="B100" s="6" t="n">
@@ -8091,7 +8663,7 @@
       </c>
       <c r="J100" s="10" t="n"/>
       <c r="K100" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L100" s="8" t="n"/>
@@ -8152,6 +8724,12 @@
         <f>IF(AH100="","",IF(U100&lt;=0,"역마진",IF(AH100&gt;=가정!$C$35,"GO",IF(AH100&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ100" s="7" t="n"/>
+      <c r="AK100" s="7" t="n"/>
+      <c r="AL100" s="6">
+        <f>IF(AK100="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK100,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="6" t="n">
@@ -8170,7 +8748,7 @@
       </c>
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L101" s="8" t="n"/>
@@ -8231,6 +8809,12 @@
         <f>IF(AH101="","",IF(U101&lt;=0,"역마진",IF(AH101&gt;=가정!$C$35,"GO",IF(AH101&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ101" s="7" t="n"/>
+      <c r="AK101" s="7" t="n"/>
+      <c r="AL101" s="6">
+        <f>IF(AK101="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK101,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="6" t="n">
@@ -8249,7 +8833,7 @@
       </c>
       <c r="J102" s="10" t="n"/>
       <c r="K102" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L102" s="8" t="n"/>
@@ -8310,6 +8894,12 @@
         <f>IF(AH102="","",IF(U102&lt;=0,"역마진",IF(AH102&gt;=가정!$C$35,"GO",IF(AH102&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ102" s="7" t="n"/>
+      <c r="AK102" s="7" t="n"/>
+      <c r="AL102" s="6">
+        <f>IF(AK102="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK102,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="6" t="n">
@@ -8328,7 +8918,7 @@
       </c>
       <c r="J103" s="10" t="n"/>
       <c r="K103" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L103" s="8" t="n"/>
@@ -8389,6 +8979,12 @@
         <f>IF(AH103="","",IF(U103&lt;=0,"역마진",IF(AH103&gt;=가정!$C$35,"GO",IF(AH103&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ103" s="7" t="n"/>
+      <c r="AK103" s="7" t="n"/>
+      <c r="AL103" s="6">
+        <f>IF(AK103="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK103,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="B104" s="6" t="n">
@@ -8407,7 +9003,7 @@
       </c>
       <c r="J104" s="10" t="n"/>
       <c r="K104" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L104" s="8" t="n"/>
@@ -8468,6 +9064,12 @@
         <f>IF(AH104="","",IF(U104&lt;=0,"역마진",IF(AH104&gt;=가정!$C$35,"GO",IF(AH104&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ104" s="7" t="n"/>
+      <c r="AK104" s="7" t="n"/>
+      <c r="AL104" s="6">
+        <f>IF(AK104="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK104,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="6" t="n">
@@ -8486,7 +9088,7 @@
       </c>
       <c r="J105" s="10" t="n"/>
       <c r="K105" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L105" s="8" t="n"/>
@@ -8547,6 +9149,12 @@
         <f>IF(AH105="","",IF(U105&lt;=0,"역마진",IF(AH105&gt;=가정!$C$35,"GO",IF(AH105&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ105" s="7" t="n"/>
+      <c r="AK105" s="7" t="n"/>
+      <c r="AL105" s="6">
+        <f>IF(AK105="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK105,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="B106" s="6" t="n">
@@ -8565,7 +9173,7 @@
       </c>
       <c r="J106" s="10" t="n"/>
       <c r="K106" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L106" s="8" t="n"/>
@@ -8626,6 +9234,12 @@
         <f>IF(AH106="","",IF(U106&lt;=0,"역마진",IF(AH106&gt;=가정!$C$35,"GO",IF(AH106&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ106" s="7" t="n"/>
+      <c r="AK106" s="7" t="n"/>
+      <c r="AL106" s="6">
+        <f>IF(AK106="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK106,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="6" t="n">
@@ -8644,7 +9258,7 @@
       </c>
       <c r="J107" s="10" t="n"/>
       <c r="K107" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L107" s="8" t="n"/>
@@ -8705,6 +9319,12 @@
         <f>IF(AH107="","",IF(U107&lt;=0,"역마진",IF(AH107&gt;=가정!$C$35,"GO",IF(AH107&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ107" s="7" t="n"/>
+      <c r="AK107" s="7" t="n"/>
+      <c r="AL107" s="6">
+        <f>IF(AK107="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK107,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="B108" s="6" t="n">
@@ -8723,7 +9343,7 @@
       </c>
       <c r="J108" s="10" t="n"/>
       <c r="K108" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L108" s="8" t="n"/>
@@ -8784,6 +9404,12 @@
         <f>IF(AH108="","",IF(U108&lt;=0,"역마진",IF(AH108&gt;=가정!$C$35,"GO",IF(AH108&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ108" s="7" t="n"/>
+      <c r="AK108" s="7" t="n"/>
+      <c r="AL108" s="6">
+        <f>IF(AK108="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK108,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="B109" s="6" t="n">
@@ -8802,7 +9428,7 @@
       </c>
       <c r="J109" s="10" t="n"/>
       <c r="K109" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L109" s="8" t="n"/>
@@ -8863,6 +9489,12 @@
         <f>IF(AH109="","",IF(U109&lt;=0,"역마진",IF(AH109&gt;=가정!$C$35,"GO",IF(AH109&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ109" s="7" t="n"/>
+      <c r="AK109" s="7" t="n"/>
+      <c r="AL109" s="6">
+        <f>IF(AK109="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK109,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="B110" s="6" t="n">
@@ -8881,7 +9513,7 @@
       </c>
       <c r="J110" s="10" t="n"/>
       <c r="K110" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L110" s="8" t="n"/>
@@ -8942,6 +9574,12 @@
         <f>IF(AH110="","",IF(U110&lt;=0,"역마진",IF(AH110&gt;=가정!$C$35,"GO",IF(AH110&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ110" s="7" t="n"/>
+      <c r="AK110" s="7" t="n"/>
+      <c r="AL110" s="6">
+        <f>IF(AK110="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK110,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="B111" s="6" t="n">
@@ -8960,7 +9598,7 @@
       </c>
       <c r="J111" s="10" t="n"/>
       <c r="K111" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L111" s="8" t="n"/>
@@ -9021,6 +9659,12 @@
         <f>IF(AH111="","",IF(U111&lt;=0,"역마진",IF(AH111&gt;=가정!$C$35,"GO",IF(AH111&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ111" s="7" t="n"/>
+      <c r="AK111" s="7" t="n"/>
+      <c r="AL111" s="6">
+        <f>IF(AK111="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK111,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="B112" s="6" t="n">
@@ -9039,7 +9683,7 @@
       </c>
       <c r="J112" s="10" t="n"/>
       <c r="K112" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L112" s="8" t="n"/>
@@ -9100,6 +9744,12 @@
         <f>IF(AH112="","",IF(U112&lt;=0,"역마진",IF(AH112&gt;=가정!$C$35,"GO",IF(AH112&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ112" s="7" t="n"/>
+      <c r="AK112" s="7" t="n"/>
+      <c r="AL112" s="6">
+        <f>IF(AK112="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK112,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="B113" s="6" t="n">
@@ -9118,7 +9768,7 @@
       </c>
       <c r="J113" s="10" t="n"/>
       <c r="K113" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L113" s="8" t="n"/>
@@ -9179,6 +9829,12 @@
         <f>IF(AH113="","",IF(U113&lt;=0,"역마진",IF(AH113&gt;=가정!$C$35,"GO",IF(AH113&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ113" s="7" t="n"/>
+      <c r="AK113" s="7" t="n"/>
+      <c r="AL113" s="6">
+        <f>IF(AK113="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK113,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="B114" s="6" t="n">
@@ -9197,7 +9853,7 @@
       </c>
       <c r="J114" s="10" t="n"/>
       <c r="K114" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L114" s="8" t="n"/>
@@ -9258,6 +9914,12 @@
         <f>IF(AH114="","",IF(U114&lt;=0,"역마진",IF(AH114&gt;=가정!$C$35,"GO",IF(AH114&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ114" s="7" t="n"/>
+      <c r="AK114" s="7" t="n"/>
+      <c r="AL114" s="6">
+        <f>IF(AK114="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK114,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="B115" s="6" t="n">
@@ -9276,7 +9938,7 @@
       </c>
       <c r="J115" s="10" t="n"/>
       <c r="K115" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L115" s="8" t="n"/>
@@ -9337,6 +9999,12 @@
         <f>IF(AH115="","",IF(U115&lt;=0,"역마진",IF(AH115&gt;=가정!$C$35,"GO",IF(AH115&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ115" s="7" t="n"/>
+      <c r="AK115" s="7" t="n"/>
+      <c r="AL115" s="6">
+        <f>IF(AK115="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK115,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="B116" s="6" t="n">
@@ -9355,7 +10023,7 @@
       </c>
       <c r="J116" s="10" t="n"/>
       <c r="K116" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L116" s="8" t="n"/>
@@ -9416,6 +10084,12 @@
         <f>IF(AH116="","",IF(U116&lt;=0,"역마진",IF(AH116&gt;=가정!$C$35,"GO",IF(AH116&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ116" s="7" t="n"/>
+      <c r="AK116" s="7" t="n"/>
+      <c r="AL116" s="6">
+        <f>IF(AK116="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK116,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="B117" s="6" t="n">
@@ -9434,7 +10108,7 @@
       </c>
       <c r="J117" s="10" t="n"/>
       <c r="K117" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L117" s="8" t="n"/>
@@ -9495,6 +10169,12 @@
         <f>IF(AH117="","",IF(U117&lt;=0,"역마진",IF(AH117&gt;=가정!$C$35,"GO",IF(AH117&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ117" s="7" t="n"/>
+      <c r="AK117" s="7" t="n"/>
+      <c r="AL117" s="6">
+        <f>IF(AK117="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK117,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="B118" s="6" t="n">
@@ -9513,7 +10193,7 @@
       </c>
       <c r="J118" s="10" t="n"/>
       <c r="K118" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L118" s="8" t="n"/>
@@ -9574,6 +10254,12 @@
         <f>IF(AH118="","",IF(U118&lt;=0,"역마진",IF(AH118&gt;=가정!$C$35,"GO",IF(AH118&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ118" s="7" t="n"/>
+      <c r="AK118" s="7" t="n"/>
+      <c r="AL118" s="6">
+        <f>IF(AK118="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK118,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="B119" s="6" t="n">
@@ -9592,7 +10278,7 @@
       </c>
       <c r="J119" s="10" t="n"/>
       <c r="K119" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L119" s="8" t="n"/>
@@ -9653,6 +10339,12 @@
         <f>IF(AH119="","",IF(U119&lt;=0,"역마진",IF(AH119&gt;=가정!$C$35,"GO",IF(AH119&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ119" s="7" t="n"/>
+      <c r="AK119" s="7" t="n"/>
+      <c r="AL119" s="6">
+        <f>IF(AK119="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK119,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="B120" s="6" t="n">
@@ -9671,7 +10363,7 @@
       </c>
       <c r="J120" s="10" t="n"/>
       <c r="K120" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L120" s="8" t="n"/>
@@ -9732,6 +10424,12 @@
         <f>IF(AH120="","",IF(U120&lt;=0,"역마진",IF(AH120&gt;=가정!$C$35,"GO",IF(AH120&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ120" s="7" t="n"/>
+      <c r="AK120" s="7" t="n"/>
+      <c r="AL120" s="6">
+        <f>IF(AK120="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK120,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="B121" s="6" t="n">
@@ -9750,7 +10448,7 @@
       </c>
       <c r="J121" s="10" t="n"/>
       <c r="K121" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L121" s="8" t="n"/>
@@ -9811,6 +10509,12 @@
         <f>IF(AH121="","",IF(U121&lt;=0,"역마진",IF(AH121&gt;=가정!$C$35,"GO",IF(AH121&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ121" s="7" t="n"/>
+      <c r="AK121" s="7" t="n"/>
+      <c r="AL121" s="6">
+        <f>IF(AK121="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK121,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="B122" s="6" t="n">
@@ -9829,7 +10533,7 @@
       </c>
       <c r="J122" s="10" t="n"/>
       <c r="K122" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L122" s="8" t="n"/>
@@ -9890,6 +10594,12 @@
         <f>IF(AH122="","",IF(U122&lt;=0,"역마진",IF(AH122&gt;=가정!$C$35,"GO",IF(AH122&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ122" s="7" t="n"/>
+      <c r="AK122" s="7" t="n"/>
+      <c r="AL122" s="6">
+        <f>IF(AK122="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK122,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="B123" s="6" t="n">
@@ -9908,7 +10618,7 @@
       </c>
       <c r="J123" s="10" t="n"/>
       <c r="K123" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L123" s="8" t="n"/>
@@ -9969,6 +10679,12 @@
         <f>IF(AH123="","",IF(U123&lt;=0,"역마진",IF(AH123&gt;=가정!$C$35,"GO",IF(AH123&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ123" s="7" t="n"/>
+      <c r="AK123" s="7" t="n"/>
+      <c r="AL123" s="6">
+        <f>IF(AK123="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK123,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="B124" s="6" t="n">
@@ -9987,7 +10703,7 @@
       </c>
       <c r="J124" s="10" t="n"/>
       <c r="K124" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L124" s="8" t="n"/>
@@ -10048,6 +10764,12 @@
         <f>IF(AH124="","",IF(U124&lt;=0,"역마진",IF(AH124&gt;=가정!$C$35,"GO",IF(AH124&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ124" s="7" t="n"/>
+      <c r="AK124" s="7" t="n"/>
+      <c r="AL124" s="6">
+        <f>IF(AK124="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK124,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="B125" s="6" t="n">
@@ -10066,7 +10788,7 @@
       </c>
       <c r="J125" s="10" t="n"/>
       <c r="K125" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L125" s="8" t="n"/>
@@ -10127,6 +10849,12 @@
         <f>IF(AH125="","",IF(U125&lt;=0,"역마진",IF(AH125&gt;=가정!$C$35,"GO",IF(AH125&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ125" s="7" t="n"/>
+      <c r="AK125" s="7" t="n"/>
+      <c r="AL125" s="6">
+        <f>IF(AK125="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK125,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="B126" s="6" t="n">
@@ -10145,7 +10873,7 @@
       </c>
       <c r="J126" s="10" t="n"/>
       <c r="K126" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L126" s="8" t="n"/>
@@ -10206,6 +10934,12 @@
         <f>IF(AH126="","",IF(U126&lt;=0,"역마진",IF(AH126&gt;=가정!$C$35,"GO",IF(AH126&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ126" s="7" t="n"/>
+      <c r="AK126" s="7" t="n"/>
+      <c r="AL126" s="6">
+        <f>IF(AK126="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK126,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="B127" s="6" t="n">
@@ -10224,7 +10958,7 @@
       </c>
       <c r="J127" s="10" t="n"/>
       <c r="K127" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L127" s="8" t="n"/>
@@ -10285,6 +11019,12 @@
         <f>IF(AH127="","",IF(U127&lt;=0,"역마진",IF(AH127&gt;=가정!$C$35,"GO",IF(AH127&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ127" s="7" t="n"/>
+      <c r="AK127" s="7" t="n"/>
+      <c r="AL127" s="6">
+        <f>IF(AK127="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK127,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="B128" s="6" t="n">
@@ -10303,7 +11043,7 @@
       </c>
       <c r="J128" s="10" t="n"/>
       <c r="K128" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L128" s="8" t="n"/>
@@ -10364,6 +11104,12 @@
         <f>IF(AH128="","",IF(U128&lt;=0,"역마진",IF(AH128&gt;=가정!$C$35,"GO",IF(AH128&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ128" s="7" t="n"/>
+      <c r="AK128" s="7" t="n"/>
+      <c r="AL128" s="6">
+        <f>IF(AK128="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK128,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="B129" s="6" t="n">
@@ -10382,7 +11128,7 @@
       </c>
       <c r="J129" s="10" t="n"/>
       <c r="K129" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L129" s="8" t="n"/>
@@ -10443,6 +11189,12 @@
         <f>IF(AH129="","",IF(U129&lt;=0,"역마진",IF(AH129&gt;=가정!$C$35,"GO",IF(AH129&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ129" s="7" t="n"/>
+      <c r="AK129" s="7" t="n"/>
+      <c r="AL129" s="6">
+        <f>IF(AK129="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK129,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="B130" s="6" t="n">
@@ -10461,7 +11213,7 @@
       </c>
       <c r="J130" s="10" t="n"/>
       <c r="K130" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L130" s="8" t="n"/>
@@ -10522,6 +11274,12 @@
         <f>IF(AH130="","",IF(U130&lt;=0,"역마진",IF(AH130&gt;=가정!$C$35,"GO",IF(AH130&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ130" s="7" t="n"/>
+      <c r="AK130" s="7" t="n"/>
+      <c r="AL130" s="6">
+        <f>IF(AK130="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK130,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="B131" s="6" t="n">
@@ -10540,7 +11298,7 @@
       </c>
       <c r="J131" s="10" t="n"/>
       <c r="K131" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L131" s="8" t="n"/>
@@ -10601,6 +11359,12 @@
         <f>IF(AH131="","",IF(U131&lt;=0,"역마진",IF(AH131&gt;=가정!$C$35,"GO",IF(AH131&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ131" s="7" t="n"/>
+      <c r="AK131" s="7" t="n"/>
+      <c r="AL131" s="6">
+        <f>IF(AK131="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK131,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="B132" s="6" t="n">
@@ -10619,7 +11383,7 @@
       </c>
       <c r="J132" s="10" t="n"/>
       <c r="K132" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L132" s="8" t="n"/>
@@ -10680,6 +11444,12 @@
         <f>IF(AH132="","",IF(U132&lt;=0,"역마진",IF(AH132&gt;=가정!$C$35,"GO",IF(AH132&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ132" s="7" t="n"/>
+      <c r="AK132" s="7" t="n"/>
+      <c r="AL132" s="6">
+        <f>IF(AK132="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK132,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="B133" s="6" t="n">
@@ -10698,7 +11468,7 @@
       </c>
       <c r="J133" s="10" t="n"/>
       <c r="K133" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L133" s="8" t="n"/>
@@ -10759,6 +11529,12 @@
         <f>IF(AH133="","",IF(U133&lt;=0,"역마진",IF(AH133&gt;=가정!$C$35,"GO",IF(AH133&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ133" s="7" t="n"/>
+      <c r="AK133" s="7" t="n"/>
+      <c r="AL133" s="6">
+        <f>IF(AK133="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK133,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="B134" s="6" t="n">
@@ -10777,7 +11553,7 @@
       </c>
       <c r="J134" s="10" t="n"/>
       <c r="K134" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L134" s="8" t="n"/>
@@ -10838,6 +11614,12 @@
         <f>IF(AH134="","",IF(U134&lt;=0,"역마진",IF(AH134&gt;=가정!$C$35,"GO",IF(AH134&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ134" s="7" t="n"/>
+      <c r="AK134" s="7" t="n"/>
+      <c r="AL134" s="6">
+        <f>IF(AK134="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK134,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="B135" s="6" t="n">
@@ -10856,7 +11638,7 @@
       </c>
       <c r="J135" s="10" t="n"/>
       <c r="K135" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L135" s="8" t="n"/>
@@ -10917,6 +11699,12 @@
         <f>IF(AH135="","",IF(U135&lt;=0,"역마진",IF(AH135&gt;=가정!$C$35,"GO",IF(AH135&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ135" s="7" t="n"/>
+      <c r="AK135" s="7" t="n"/>
+      <c r="AL135" s="6">
+        <f>IF(AK135="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK135,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="B136" s="6" t="n">
@@ -10935,7 +11723,7 @@
       </c>
       <c r="J136" s="10" t="n"/>
       <c r="K136" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L136" s="8" t="n"/>
@@ -10996,6 +11784,12 @@
         <f>IF(AH136="","",IF(U136&lt;=0,"역마진",IF(AH136&gt;=가정!$C$35,"GO",IF(AH136&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ136" s="7" t="n"/>
+      <c r="AK136" s="7" t="n"/>
+      <c r="AL136" s="6">
+        <f>IF(AK136="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK136,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="B137" s="6" t="n">
@@ -11014,7 +11808,7 @@
       </c>
       <c r="J137" s="10" t="n"/>
       <c r="K137" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L137" s="8" t="n"/>
@@ -11075,6 +11869,12 @@
         <f>IF(AH137="","",IF(U137&lt;=0,"역마진",IF(AH137&gt;=가정!$C$35,"GO",IF(AH137&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ137" s="7" t="n"/>
+      <c r="AK137" s="7" t="n"/>
+      <c r="AL137" s="6">
+        <f>IF(AK137="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK137,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="B138" s="6" t="n">
@@ -11093,7 +11893,7 @@
       </c>
       <c r="J138" s="10" t="n"/>
       <c r="K138" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L138" s="8" t="n"/>
@@ -11154,6 +11954,12 @@
         <f>IF(AH138="","",IF(U138&lt;=0,"역마진",IF(AH138&gt;=가정!$C$35,"GO",IF(AH138&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ138" s="7" t="n"/>
+      <c r="AK138" s="7" t="n"/>
+      <c r="AL138" s="6">
+        <f>IF(AK138="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK138,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="B139" s="6" t="n">
@@ -11172,7 +11978,7 @@
       </c>
       <c r="J139" s="10" t="n"/>
       <c r="K139" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L139" s="8" t="n"/>
@@ -11233,6 +12039,12 @@
         <f>IF(AH139="","",IF(U139&lt;=0,"역마진",IF(AH139&gt;=가정!$C$35,"GO",IF(AH139&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ139" s="7" t="n"/>
+      <c r="AK139" s="7" t="n"/>
+      <c r="AL139" s="6">
+        <f>IF(AK139="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK139,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="B140" s="6" t="n">
@@ -11251,7 +12063,7 @@
       </c>
       <c r="J140" s="10" t="n"/>
       <c r="K140" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L140" s="8" t="n"/>
@@ -11312,6 +12124,12 @@
         <f>IF(AH140="","",IF(U140&lt;=0,"역마진",IF(AH140&gt;=가정!$C$35,"GO",IF(AH140&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ140" s="7" t="n"/>
+      <c r="AK140" s="7" t="n"/>
+      <c r="AL140" s="6">
+        <f>IF(AK140="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK140,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="B141" s="6" t="n">
@@ -11330,7 +12148,7 @@
       </c>
       <c r="J141" s="10" t="n"/>
       <c r="K141" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L141" s="8" t="n"/>
@@ -11391,6 +12209,12 @@
         <f>IF(AH141="","",IF(U141&lt;=0,"역마진",IF(AH141&gt;=가정!$C$35,"GO",IF(AH141&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ141" s="7" t="n"/>
+      <c r="AK141" s="7" t="n"/>
+      <c r="AL141" s="6">
+        <f>IF(AK141="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK141,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="B142" s="6" t="n">
@@ -11409,7 +12233,7 @@
       </c>
       <c r="J142" s="10" t="n"/>
       <c r="K142" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L142" s="8" t="n"/>
@@ -11470,6 +12294,12 @@
         <f>IF(AH142="","",IF(U142&lt;=0,"역마진",IF(AH142&gt;=가정!$C$35,"GO",IF(AH142&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ142" s="7" t="n"/>
+      <c r="AK142" s="7" t="n"/>
+      <c r="AL142" s="6">
+        <f>IF(AK142="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK142,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="B143" s="6" t="n">
@@ -11488,7 +12318,7 @@
       </c>
       <c r="J143" s="10" t="n"/>
       <c r="K143" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L143" s="8" t="n"/>
@@ -11549,6 +12379,12 @@
         <f>IF(AH143="","",IF(U143&lt;=0,"역마진",IF(AH143&gt;=가정!$C$35,"GO",IF(AH143&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ143" s="7" t="n"/>
+      <c r="AK143" s="7" t="n"/>
+      <c r="AL143" s="6">
+        <f>IF(AK143="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK143,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="B144" s="6" t="n">
@@ -11567,7 +12403,7 @@
       </c>
       <c r="J144" s="10" t="n"/>
       <c r="K144" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L144" s="8" t="n"/>
@@ -11628,6 +12464,12 @@
         <f>IF(AH144="","",IF(U144&lt;=0,"역마진",IF(AH144&gt;=가정!$C$35,"GO",IF(AH144&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ144" s="7" t="n"/>
+      <c r="AK144" s="7" t="n"/>
+      <c r="AL144" s="6">
+        <f>IF(AK144="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK144,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="B145" s="6" t="n">
@@ -11646,7 +12488,7 @@
       </c>
       <c r="J145" s="10" t="n"/>
       <c r="K145" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L145" s="8" t="n"/>
@@ -11707,6 +12549,12 @@
         <f>IF(AH145="","",IF(U145&lt;=0,"역마진",IF(AH145&gt;=가정!$C$35,"GO",IF(AH145&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ145" s="7" t="n"/>
+      <c r="AK145" s="7" t="n"/>
+      <c r="AL145" s="6">
+        <f>IF(AK145="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK145,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="B146" s="6" t="n">
@@ -11725,7 +12573,7 @@
       </c>
       <c r="J146" s="10" t="n"/>
       <c r="K146" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L146" s="8" t="n"/>
@@ -11786,6 +12634,12 @@
         <f>IF(AH146="","",IF(U146&lt;=0,"역마진",IF(AH146&gt;=가정!$C$35,"GO",IF(AH146&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ146" s="7" t="n"/>
+      <c r="AK146" s="7" t="n"/>
+      <c r="AL146" s="6">
+        <f>IF(AK146="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK146,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="B147" s="6" t="n">
@@ -11804,7 +12658,7 @@
       </c>
       <c r="J147" s="10" t="n"/>
       <c r="K147" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L147" s="8" t="n"/>
@@ -11865,6 +12719,12 @@
         <f>IF(AH147="","",IF(U147&lt;=0,"역마진",IF(AH147&gt;=가정!$C$35,"GO",IF(AH147&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ147" s="7" t="n"/>
+      <c r="AK147" s="7" t="n"/>
+      <c r="AL147" s="6">
+        <f>IF(AK147="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK147,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="B148" s="6" t="n">
@@ -11883,7 +12743,7 @@
       </c>
       <c r="J148" s="10" t="n"/>
       <c r="K148" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L148" s="8" t="n"/>
@@ -11944,6 +12804,12 @@
         <f>IF(AH148="","",IF(U148&lt;=0,"역마진",IF(AH148&gt;=가정!$C$35,"GO",IF(AH148&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ148" s="7" t="n"/>
+      <c r="AK148" s="7" t="n"/>
+      <c r="AL148" s="6">
+        <f>IF(AK148="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK148,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="B149" s="6" t="n">
@@ -11962,7 +12828,7 @@
       </c>
       <c r="J149" s="10" t="n"/>
       <c r="K149" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L149" s="8" t="n"/>
@@ -12023,6 +12889,12 @@
         <f>IF(AH149="","",IF(U149&lt;=0,"역마진",IF(AH149&gt;=가정!$C$35,"GO",IF(AH149&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ149" s="7" t="n"/>
+      <c r="AK149" s="7" t="n"/>
+      <c r="AL149" s="6">
+        <f>IF(AK149="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK149,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="B150" s="6" t="n">
@@ -12041,7 +12913,7 @@
       </c>
       <c r="J150" s="10" t="n"/>
       <c r="K150" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L150" s="8" t="n"/>
@@ -12102,6 +12974,12 @@
         <f>IF(AH150="","",IF(U150&lt;=0,"역마진",IF(AH150&gt;=가정!$C$35,"GO",IF(AH150&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ150" s="7" t="n"/>
+      <c r="AK150" s="7" t="n"/>
+      <c r="AL150" s="6">
+        <f>IF(AK150="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK150,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="B151" s="6" t="n">
@@ -12120,7 +12998,7 @@
       </c>
       <c r="J151" s="10" t="n"/>
       <c r="K151" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L151" s="8" t="n"/>
@@ -12181,6 +13059,12 @@
         <f>IF(AH151="","",IF(U151&lt;=0,"역마진",IF(AH151&gt;=가정!$C$35,"GO",IF(AH151&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ151" s="7" t="n"/>
+      <c r="AK151" s="7" t="n"/>
+      <c r="AL151" s="6">
+        <f>IF(AK151="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK151,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="B152" s="6" t="n">
@@ -12199,7 +13083,7 @@
       </c>
       <c r="J152" s="10" t="n"/>
       <c r="K152" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L152" s="8" t="n"/>
@@ -12260,6 +13144,12 @@
         <f>IF(AH152="","",IF(U152&lt;=0,"역마진",IF(AH152&gt;=가정!$C$35,"GO",IF(AH152&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ152" s="7" t="n"/>
+      <c r="AK152" s="7" t="n"/>
+      <c r="AL152" s="6">
+        <f>IF(AK152="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK152,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="B153" s="6" t="n">
@@ -12278,7 +13168,7 @@
       </c>
       <c r="J153" s="10" t="n"/>
       <c r="K153" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L153" s="8" t="n"/>
@@ -12339,6 +13229,12 @@
         <f>IF(AH153="","",IF(U153&lt;=0,"역마진",IF(AH153&gt;=가정!$C$35,"GO",IF(AH153&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ153" s="7" t="n"/>
+      <c r="AK153" s="7" t="n"/>
+      <c r="AL153" s="6">
+        <f>IF(AK153="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK153,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="B154" s="6" t="n">
@@ -12357,7 +13253,7 @@
       </c>
       <c r="J154" s="10" t="n"/>
       <c r="K154" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L154" s="8" t="n"/>
@@ -12418,6 +13314,12 @@
         <f>IF(AH154="","",IF(U154&lt;=0,"역마진",IF(AH154&gt;=가정!$C$35,"GO",IF(AH154&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ154" s="7" t="n"/>
+      <c r="AK154" s="7" t="n"/>
+      <c r="AL154" s="6">
+        <f>IF(AK154="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK154,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="B155" s="6" t="n">
@@ -12436,7 +13338,7 @@
       </c>
       <c r="J155" s="10" t="n"/>
       <c r="K155" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L155" s="8" t="n"/>
@@ -12497,6 +13399,12 @@
         <f>IF(AH155="","",IF(U155&lt;=0,"역마진",IF(AH155&gt;=가정!$C$35,"GO",IF(AH155&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ155" s="7" t="n"/>
+      <c r="AK155" s="7" t="n"/>
+      <c r="AL155" s="6">
+        <f>IF(AK155="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK155,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="B156" s="6" t="n">
@@ -12515,7 +13423,7 @@
       </c>
       <c r="J156" s="10" t="n"/>
       <c r="K156" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L156" s="8" t="n"/>
@@ -12576,6 +13484,12 @@
         <f>IF(AH156="","",IF(U156&lt;=0,"역마진",IF(AH156&gt;=가정!$C$35,"GO",IF(AH156&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ156" s="7" t="n"/>
+      <c r="AK156" s="7" t="n"/>
+      <c r="AL156" s="6">
+        <f>IF(AK156="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK156,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="B157" s="6" t="n">
@@ -12594,7 +13508,7 @@
       </c>
       <c r="J157" s="10" t="n"/>
       <c r="K157" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L157" s="8" t="n"/>
@@ -12655,6 +13569,12 @@
         <f>IF(AH157="","",IF(U157&lt;=0,"역마진",IF(AH157&gt;=가정!$C$35,"GO",IF(AH157&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ157" s="7" t="n"/>
+      <c r="AK157" s="7" t="n"/>
+      <c r="AL157" s="6">
+        <f>IF(AK157="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK157,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="B158" s="6" t="n">
@@ -12673,7 +13593,7 @@
       </c>
       <c r="J158" s="10" t="n"/>
       <c r="K158" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L158" s="8" t="n"/>
@@ -12734,6 +13654,12 @@
         <f>IF(AH158="","",IF(U158&lt;=0,"역마진",IF(AH158&gt;=가정!$C$35,"GO",IF(AH158&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ158" s="7" t="n"/>
+      <c r="AK158" s="7" t="n"/>
+      <c r="AL158" s="6">
+        <f>IF(AK158="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK158,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="B159" s="6" t="n">
@@ -12752,7 +13678,7 @@
       </c>
       <c r="J159" s="10" t="n"/>
       <c r="K159" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L159" s="8" t="n"/>
@@ -12813,6 +13739,12 @@
         <f>IF(AH159="","",IF(U159&lt;=0,"역마진",IF(AH159&gt;=가정!$C$35,"GO",IF(AH159&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ159" s="7" t="n"/>
+      <c r="AK159" s="7" t="n"/>
+      <c r="AL159" s="6">
+        <f>IF(AK159="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK159,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="B160" s="6" t="n">
@@ -12831,7 +13763,7 @@
       </c>
       <c r="J160" s="10" t="n"/>
       <c r="K160" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L160" s="8" t="n"/>
@@ -12892,6 +13824,12 @@
         <f>IF(AH160="","",IF(U160&lt;=0,"역마진",IF(AH160&gt;=가정!$C$35,"GO",IF(AH160&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ160" s="7" t="n"/>
+      <c r="AK160" s="7" t="n"/>
+      <c r="AL160" s="6">
+        <f>IF(AK160="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK160,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="B161" s="6" t="n">
@@ -12910,7 +13848,7 @@
       </c>
       <c r="J161" s="10" t="n"/>
       <c r="K161" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L161" s="8" t="n"/>
@@ -12971,6 +13909,12 @@
         <f>IF(AH161="","",IF(U161&lt;=0,"역마진",IF(AH161&gt;=가정!$C$35,"GO",IF(AH161&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ161" s="7" t="n"/>
+      <c r="AK161" s="7" t="n"/>
+      <c r="AL161" s="6">
+        <f>IF(AK161="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK161,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="B162" s="6" t="n">
@@ -12989,7 +13933,7 @@
       </c>
       <c r="J162" s="10" t="n"/>
       <c r="K162" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L162" s="8" t="n"/>
@@ -13050,6 +13994,12 @@
         <f>IF(AH162="","",IF(U162&lt;=0,"역마진",IF(AH162&gt;=가정!$C$35,"GO",IF(AH162&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ162" s="7" t="n"/>
+      <c r="AK162" s="7" t="n"/>
+      <c r="AL162" s="6">
+        <f>IF(AK162="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK162,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="B163" s="6" t="n">
@@ -13068,7 +14018,7 @@
       </c>
       <c r="J163" s="10" t="n"/>
       <c r="K163" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L163" s="8" t="n"/>
@@ -13129,6 +14079,12 @@
         <f>IF(AH163="","",IF(U163&lt;=0,"역마진",IF(AH163&gt;=가정!$C$35,"GO",IF(AH163&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ163" s="7" t="n"/>
+      <c r="AK163" s="7" t="n"/>
+      <c r="AL163" s="6">
+        <f>IF(AK163="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK163,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="B164" s="6" t="n">
@@ -13147,7 +14103,7 @@
       </c>
       <c r="J164" s="10" t="n"/>
       <c r="K164" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L164" s="8" t="n"/>
@@ -13208,6 +14164,12 @@
         <f>IF(AH164="","",IF(U164&lt;=0,"역마진",IF(AH164&gt;=가정!$C$35,"GO",IF(AH164&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ164" s="7" t="n"/>
+      <c r="AK164" s="7" t="n"/>
+      <c r="AL164" s="6">
+        <f>IF(AK164="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK164,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="B165" s="6" t="n">
@@ -13226,7 +14188,7 @@
       </c>
       <c r="J165" s="10" t="n"/>
       <c r="K165" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L165" s="8" t="n"/>
@@ -13287,6 +14249,12 @@
         <f>IF(AH165="","",IF(U165&lt;=0,"역마진",IF(AH165&gt;=가정!$C$35,"GO",IF(AH165&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ165" s="7" t="n"/>
+      <c r="AK165" s="7" t="n"/>
+      <c r="AL165" s="6">
+        <f>IF(AK165="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK165,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="B166" s="6" t="n">
@@ -13305,7 +14273,7 @@
       </c>
       <c r="J166" s="10" t="n"/>
       <c r="K166" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L166" s="8" t="n"/>
@@ -13366,6 +14334,12 @@
         <f>IF(AH166="","",IF(U166&lt;=0,"역마진",IF(AH166&gt;=가정!$C$35,"GO",IF(AH166&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ166" s="7" t="n"/>
+      <c r="AK166" s="7" t="n"/>
+      <c r="AL166" s="6">
+        <f>IF(AK166="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK166,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="B167" s="6" t="n">
@@ -13384,7 +14358,7 @@
       </c>
       <c r="J167" s="10" t="n"/>
       <c r="K167" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L167" s="8" t="n"/>
@@ -13445,6 +14419,12 @@
         <f>IF(AH167="","",IF(U167&lt;=0,"역마진",IF(AH167&gt;=가정!$C$35,"GO",IF(AH167&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ167" s="7" t="n"/>
+      <c r="AK167" s="7" t="n"/>
+      <c r="AL167" s="6">
+        <f>IF(AK167="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK167,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="B168" s="6" t="n">
@@ -13463,7 +14443,7 @@
       </c>
       <c r="J168" s="10" t="n"/>
       <c r="K168" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L168" s="8" t="n"/>
@@ -13524,6 +14504,12 @@
         <f>IF(AH168="","",IF(U168&lt;=0,"역마진",IF(AH168&gt;=가정!$C$35,"GO",IF(AH168&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ168" s="7" t="n"/>
+      <c r="AK168" s="7" t="n"/>
+      <c r="AL168" s="6">
+        <f>IF(AK168="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK168,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="B169" s="6" t="n">
@@ -13542,7 +14528,7 @@
       </c>
       <c r="J169" s="10" t="n"/>
       <c r="K169" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L169" s="8" t="n"/>
@@ -13603,6 +14589,12 @@
         <f>IF(AH169="","",IF(U169&lt;=0,"역마진",IF(AH169&gt;=가정!$C$35,"GO",IF(AH169&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ169" s="7" t="n"/>
+      <c r="AK169" s="7" t="n"/>
+      <c r="AL169" s="6">
+        <f>IF(AK169="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK169,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="B170" s="6" t="n">
@@ -13621,7 +14613,7 @@
       </c>
       <c r="J170" s="10" t="n"/>
       <c r="K170" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L170" s="8" t="n"/>
@@ -13682,6 +14674,12 @@
         <f>IF(AH170="","",IF(U170&lt;=0,"역마진",IF(AH170&gt;=가정!$C$35,"GO",IF(AH170&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ170" s="7" t="n"/>
+      <c r="AK170" s="7" t="n"/>
+      <c r="AL170" s="6">
+        <f>IF(AK170="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK170,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="B171" s="6" t="n">
@@ -13700,7 +14698,7 @@
       </c>
       <c r="J171" s="10" t="n"/>
       <c r="K171" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L171" s="8" t="n"/>
@@ -13761,6 +14759,12 @@
         <f>IF(AH171="","",IF(U171&lt;=0,"역마진",IF(AH171&gt;=가정!$C$35,"GO",IF(AH171&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ171" s="7" t="n"/>
+      <c r="AK171" s="7" t="n"/>
+      <c r="AL171" s="6">
+        <f>IF(AK171="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK171,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="B172" s="6" t="n">
@@ -13779,7 +14783,7 @@
       </c>
       <c r="J172" s="10" t="n"/>
       <c r="K172" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L172" s="8" t="n"/>
@@ -13840,6 +14844,12 @@
         <f>IF(AH172="","",IF(U172&lt;=0,"역마진",IF(AH172&gt;=가정!$C$35,"GO",IF(AH172&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ172" s="7" t="n"/>
+      <c r="AK172" s="7" t="n"/>
+      <c r="AL172" s="6">
+        <f>IF(AK172="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK172,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="B173" s="6" t="n">
@@ -13858,7 +14868,7 @@
       </c>
       <c r="J173" s="10" t="n"/>
       <c r="K173" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L173" s="8" t="n"/>
@@ -13919,6 +14929,12 @@
         <f>IF(AH173="","",IF(U173&lt;=0,"역마진",IF(AH173&gt;=가정!$C$35,"GO",IF(AH173&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ173" s="7" t="n"/>
+      <c r="AK173" s="7" t="n"/>
+      <c r="AL173" s="6">
+        <f>IF(AK173="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK173,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="B174" s="6" t="n">
@@ -13937,7 +14953,7 @@
       </c>
       <c r="J174" s="10" t="n"/>
       <c r="K174" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L174" s="8" t="n"/>
@@ -13998,6 +15014,12 @@
         <f>IF(AH174="","",IF(U174&lt;=0,"역마진",IF(AH174&gt;=가정!$C$35,"GO",IF(AH174&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ174" s="7" t="n"/>
+      <c r="AK174" s="7" t="n"/>
+      <c r="AL174" s="6">
+        <f>IF(AK174="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK174,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="B175" s="6" t="n">
@@ -14016,7 +15038,7 @@
       </c>
       <c r="J175" s="10" t="n"/>
       <c r="K175" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L175" s="8" t="n"/>
@@ -14077,6 +15099,12 @@
         <f>IF(AH175="","",IF(U175&lt;=0,"역마진",IF(AH175&gt;=가정!$C$35,"GO",IF(AH175&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ175" s="7" t="n"/>
+      <c r="AK175" s="7" t="n"/>
+      <c r="AL175" s="6">
+        <f>IF(AK175="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK175,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="B176" s="6" t="n">
@@ -14095,7 +15123,7 @@
       </c>
       <c r="J176" s="10" t="n"/>
       <c r="K176" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L176" s="8" t="n"/>
@@ -14156,6 +15184,12 @@
         <f>IF(AH176="","",IF(U176&lt;=0,"역마진",IF(AH176&gt;=가정!$C$35,"GO",IF(AH176&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ176" s="7" t="n"/>
+      <c r="AK176" s="7" t="n"/>
+      <c r="AL176" s="6">
+        <f>IF(AK176="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK176,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="B177" s="6" t="n">
@@ -14174,7 +15208,7 @@
       </c>
       <c r="J177" s="10" t="n"/>
       <c r="K177" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L177" s="8" t="n"/>
@@ -14235,6 +15269,12 @@
         <f>IF(AH177="","",IF(U177&lt;=0,"역마진",IF(AH177&gt;=가정!$C$35,"GO",IF(AH177&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ177" s="7" t="n"/>
+      <c r="AK177" s="7" t="n"/>
+      <c r="AL177" s="6">
+        <f>IF(AK177="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK177,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="B178" s="6" t="n">
@@ -14253,7 +15293,7 @@
       </c>
       <c r="J178" s="10" t="n"/>
       <c r="K178" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L178" s="8" t="n"/>
@@ -14314,6 +15354,12 @@
         <f>IF(AH178="","",IF(U178&lt;=0,"역마진",IF(AH178&gt;=가정!$C$35,"GO",IF(AH178&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ178" s="7" t="n"/>
+      <c r="AK178" s="7" t="n"/>
+      <c r="AL178" s="6">
+        <f>IF(AK178="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK178,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="B179" s="6" t="n">
@@ -14332,7 +15378,7 @@
       </c>
       <c r="J179" s="10" t="n"/>
       <c r="K179" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L179" s="8" t="n"/>
@@ -14393,6 +15439,12 @@
         <f>IF(AH179="","",IF(U179&lt;=0,"역마진",IF(AH179&gt;=가정!$C$35,"GO",IF(AH179&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ179" s="7" t="n"/>
+      <c r="AK179" s="7" t="n"/>
+      <c r="AL179" s="6">
+        <f>IF(AK179="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK179,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="B180" s="6" t="n">
@@ -14411,7 +15463,7 @@
       </c>
       <c r="J180" s="10" t="n"/>
       <c r="K180" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L180" s="8" t="n"/>
@@ -14472,6 +15524,12 @@
         <f>IF(AH180="","",IF(U180&lt;=0,"역마진",IF(AH180&gt;=가정!$C$35,"GO",IF(AH180&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ180" s="7" t="n"/>
+      <c r="AK180" s="7" t="n"/>
+      <c r="AL180" s="6">
+        <f>IF(AK180="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK180,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="B181" s="6" t="n">
@@ -14490,7 +15548,7 @@
       </c>
       <c r="J181" s="10" t="n"/>
       <c r="K181" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L181" s="8" t="n"/>
@@ -14551,6 +15609,12 @@
         <f>IF(AH181="","",IF(U181&lt;=0,"역마진",IF(AH181&gt;=가정!$C$35,"GO",IF(AH181&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ181" s="7" t="n"/>
+      <c r="AK181" s="7" t="n"/>
+      <c r="AL181" s="6">
+        <f>IF(AK181="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK181,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="B182" s="6" t="n">
@@ -14569,7 +15633,7 @@
       </c>
       <c r="J182" s="10" t="n"/>
       <c r="K182" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L182" s="8" t="n"/>
@@ -14630,6 +15694,12 @@
         <f>IF(AH182="","",IF(U182&lt;=0,"역마진",IF(AH182&gt;=가정!$C$35,"GO",IF(AH182&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ182" s="7" t="n"/>
+      <c r="AK182" s="7" t="n"/>
+      <c r="AL182" s="6">
+        <f>IF(AK182="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK182,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="B183" s="6" t="n">
@@ -14648,7 +15718,7 @@
       </c>
       <c r="J183" s="10" t="n"/>
       <c r="K183" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L183" s="8" t="n"/>
@@ -14709,6 +15779,12 @@
         <f>IF(AH183="","",IF(U183&lt;=0,"역마진",IF(AH183&gt;=가정!$C$35,"GO",IF(AH183&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ183" s="7" t="n"/>
+      <c r="AK183" s="7" t="n"/>
+      <c r="AL183" s="6">
+        <f>IF(AK183="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK183,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="B184" s="6" t="n">
@@ -14727,7 +15803,7 @@
       </c>
       <c r="J184" s="10" t="n"/>
       <c r="K184" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L184" s="8" t="n"/>
@@ -14788,6 +15864,12 @@
         <f>IF(AH184="","",IF(U184&lt;=0,"역마진",IF(AH184&gt;=가정!$C$35,"GO",IF(AH184&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ184" s="7" t="n"/>
+      <c r="AK184" s="7" t="n"/>
+      <c r="AL184" s="6">
+        <f>IF(AK184="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK184,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="B185" s="6" t="n">
@@ -14806,7 +15888,7 @@
       </c>
       <c r="J185" s="10" t="n"/>
       <c r="K185" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L185" s="8" t="n"/>
@@ -14867,6 +15949,12 @@
         <f>IF(AH185="","",IF(U185&lt;=0,"역마진",IF(AH185&gt;=가정!$C$35,"GO",IF(AH185&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ185" s="7" t="n"/>
+      <c r="AK185" s="7" t="n"/>
+      <c r="AL185" s="6">
+        <f>IF(AK185="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK185,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="B186" s="6" t="n">
@@ -14885,7 +15973,7 @@
       </c>
       <c r="J186" s="10" t="n"/>
       <c r="K186" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L186" s="8" t="n"/>
@@ -14946,6 +16034,12 @@
         <f>IF(AH186="","",IF(U186&lt;=0,"역마진",IF(AH186&gt;=가정!$C$35,"GO",IF(AH186&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ186" s="7" t="n"/>
+      <c r="AK186" s="7" t="n"/>
+      <c r="AL186" s="6">
+        <f>IF(AK186="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK186,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="B187" s="6" t="n">
@@ -14964,7 +16058,7 @@
       </c>
       <c r="J187" s="10" t="n"/>
       <c r="K187" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L187" s="8" t="n"/>
@@ -15025,6 +16119,12 @@
         <f>IF(AH187="","",IF(U187&lt;=0,"역마진",IF(AH187&gt;=가정!$C$35,"GO",IF(AH187&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ187" s="7" t="n"/>
+      <c r="AK187" s="7" t="n"/>
+      <c r="AL187" s="6">
+        <f>IF(AK187="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK187,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="B188" s="6" t="n">
@@ -15043,7 +16143,7 @@
       </c>
       <c r="J188" s="10" t="n"/>
       <c r="K188" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L188" s="8" t="n"/>
@@ -15104,6 +16204,12 @@
         <f>IF(AH188="","",IF(U188&lt;=0,"역마진",IF(AH188&gt;=가정!$C$35,"GO",IF(AH188&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ188" s="7" t="n"/>
+      <c r="AK188" s="7" t="n"/>
+      <c r="AL188" s="6">
+        <f>IF(AK188="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK188,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="B189" s="6" t="n">
@@ -15122,7 +16228,7 @@
       </c>
       <c r="J189" s="10" t="n"/>
       <c r="K189" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L189" s="8" t="n"/>
@@ -15183,6 +16289,12 @@
         <f>IF(AH189="","",IF(U189&lt;=0,"역마진",IF(AH189&gt;=가정!$C$35,"GO",IF(AH189&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ189" s="7" t="n"/>
+      <c r="AK189" s="7" t="n"/>
+      <c r="AL189" s="6">
+        <f>IF(AK189="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK189,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="B190" s="6" t="n">
@@ -15201,7 +16313,7 @@
       </c>
       <c r="J190" s="10" t="n"/>
       <c r="K190" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L190" s="8" t="n"/>
@@ -15262,6 +16374,12 @@
         <f>IF(AH190="","",IF(U190&lt;=0,"역마진",IF(AH190&gt;=가정!$C$35,"GO",IF(AH190&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ190" s="7" t="n"/>
+      <c r="AK190" s="7" t="n"/>
+      <c r="AL190" s="6">
+        <f>IF(AK190="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK190,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="B191" s="6" t="n">
@@ -15280,7 +16398,7 @@
       </c>
       <c r="J191" s="10" t="n"/>
       <c r="K191" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L191" s="8" t="n"/>
@@ -15341,6 +16459,12 @@
         <f>IF(AH191="","",IF(U191&lt;=0,"역마진",IF(AH191&gt;=가정!$C$35,"GO",IF(AH191&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ191" s="7" t="n"/>
+      <c r="AK191" s="7" t="n"/>
+      <c r="AL191" s="6">
+        <f>IF(AK191="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK191,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="B192" s="6" t="n">
@@ -15359,7 +16483,7 @@
       </c>
       <c r="J192" s="10" t="n"/>
       <c r="K192" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L192" s="8" t="n"/>
@@ -15420,6 +16544,12 @@
         <f>IF(AH192="","",IF(U192&lt;=0,"역마진",IF(AH192&gt;=가정!$C$35,"GO",IF(AH192&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ192" s="7" t="n"/>
+      <c r="AK192" s="7" t="n"/>
+      <c r="AL192" s="6">
+        <f>IF(AK192="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK192,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="B193" s="6" t="n">
@@ -15438,7 +16568,7 @@
       </c>
       <c r="J193" s="10" t="n"/>
       <c r="K193" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L193" s="8" t="n"/>
@@ -15499,6 +16629,12 @@
         <f>IF(AH193="","",IF(U193&lt;=0,"역마진",IF(AH193&gt;=가정!$C$35,"GO",IF(AH193&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ193" s="7" t="n"/>
+      <c r="AK193" s="7" t="n"/>
+      <c r="AL193" s="6">
+        <f>IF(AK193="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK193,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="B194" s="6" t="n">
@@ -15517,7 +16653,7 @@
       </c>
       <c r="J194" s="10" t="n"/>
       <c r="K194" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L194" s="8" t="n"/>
@@ -15578,6 +16714,12 @@
         <f>IF(AH194="","",IF(U194&lt;=0,"역마진",IF(AH194&gt;=가정!$C$35,"GO",IF(AH194&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ194" s="7" t="n"/>
+      <c r="AK194" s="7" t="n"/>
+      <c r="AL194" s="6">
+        <f>IF(AK194="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK194,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="B195" s="6" t="n">
@@ -15596,7 +16738,7 @@
       </c>
       <c r="J195" s="10" t="n"/>
       <c r="K195" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L195" s="8" t="n"/>
@@ -15657,6 +16799,12 @@
         <f>IF(AH195="","",IF(U195&lt;=0,"역마진",IF(AH195&gt;=가정!$C$35,"GO",IF(AH195&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ195" s="7" t="n"/>
+      <c r="AK195" s="7" t="n"/>
+      <c r="AL195" s="6">
+        <f>IF(AK195="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK195,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="B196" s="6" t="n">
@@ -15675,7 +16823,7 @@
       </c>
       <c r="J196" s="10" t="n"/>
       <c r="K196" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L196" s="8" t="n"/>
@@ -15736,6 +16884,12 @@
         <f>IF(AH196="","",IF(U196&lt;=0,"역마진",IF(AH196&gt;=가정!$C$35,"GO",IF(AH196&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ196" s="7" t="n"/>
+      <c r="AK196" s="7" t="n"/>
+      <c r="AL196" s="6">
+        <f>IF(AK196="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK196,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="B197" s="6" t="n">
@@ -15754,7 +16908,7 @@
       </c>
       <c r="J197" s="10" t="n"/>
       <c r="K197" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L197" s="8" t="n"/>
@@ -15815,6 +16969,12 @@
         <f>IF(AH197="","",IF(U197&lt;=0,"역마진",IF(AH197&gt;=가정!$C$35,"GO",IF(AH197&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ197" s="7" t="n"/>
+      <c r="AK197" s="7" t="n"/>
+      <c r="AL197" s="6">
+        <f>IF(AK197="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK197,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="B198" s="6" t="n">
@@ -15833,7 +16993,7 @@
       </c>
       <c r="J198" s="10" t="n"/>
       <c r="K198" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L198" s="8" t="n"/>
@@ -15894,6 +17054,12 @@
         <f>IF(AH198="","",IF(U198&lt;=0,"역마진",IF(AH198&gt;=가정!$C$35,"GO",IF(AH198&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ198" s="7" t="n"/>
+      <c r="AK198" s="7" t="n"/>
+      <c r="AL198" s="6">
+        <f>IF(AK198="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK198,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="B199" s="6" t="n">
@@ -15912,7 +17078,7 @@
       </c>
       <c r="J199" s="10" t="n"/>
       <c r="K199" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L199" s="8" t="n"/>
@@ -15973,6 +17139,12 @@
         <f>IF(AH199="","",IF(U199&lt;=0,"역마진",IF(AH199&gt;=가정!$C$35,"GO",IF(AH199&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ199" s="7" t="n"/>
+      <c r="AK199" s="7" t="n"/>
+      <c r="AL199" s="6">
+        <f>IF(AK199="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK199,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="B200" s="6" t="n">
@@ -15991,7 +17163,7 @@
       </c>
       <c r="J200" s="10" t="n"/>
       <c r="K200" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L200" s="8" t="n"/>
@@ -16052,6 +17224,12 @@
         <f>IF(AH200="","",IF(U200&lt;=0,"역마진",IF(AH200&gt;=가정!$C$35,"GO",IF(AH200&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ200" s="7" t="n"/>
+      <c r="AK200" s="7" t="n"/>
+      <c r="AL200" s="6">
+        <f>IF(AK200="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK200,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="B201" s="6" t="n">
@@ -16070,7 +17248,7 @@
       </c>
       <c r="J201" s="10" t="n"/>
       <c r="K201" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L201" s="8" t="n"/>
@@ -16131,6 +17309,12 @@
         <f>IF(AH201="","",IF(U201&lt;=0,"역마진",IF(AH201&gt;=가정!$C$35,"GO",IF(AH201&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ201" s="7" t="n"/>
+      <c r="AK201" s="7" t="n"/>
+      <c r="AL201" s="6">
+        <f>IF(AK201="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK201,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="B202" s="6" t="n">
@@ -16149,7 +17333,7 @@
       </c>
       <c r="J202" s="10" t="n"/>
       <c r="K202" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L202" s="8" t="n"/>
@@ -16210,6 +17394,12 @@
         <f>IF(AH202="","",IF(U202&lt;=0,"역마진",IF(AH202&gt;=가정!$C$35,"GO",IF(AH202&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ202" s="7" t="n"/>
+      <c r="AK202" s="7" t="n"/>
+      <c r="AL202" s="6">
+        <f>IF(AK202="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK202,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="B203" s="6" t="n">
@@ -16228,7 +17418,7 @@
       </c>
       <c r="J203" s="10" t="n"/>
       <c r="K203" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L203" s="8" t="n"/>
@@ -16289,6 +17479,12 @@
         <f>IF(AH203="","",IF(U203&lt;=0,"역마진",IF(AH203&gt;=가정!$C$35,"GO",IF(AH203&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ203" s="7" t="n"/>
+      <c r="AK203" s="7" t="n"/>
+      <c r="AL203" s="6">
+        <f>IF(AK203="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK203,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="B204" s="6" t="n">
@@ -16307,7 +17503,7 @@
       </c>
       <c r="J204" s="10" t="n"/>
       <c r="K204" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L204" s="8" t="n"/>
@@ -16368,6 +17564,12 @@
         <f>IF(AH204="","",IF(U204&lt;=0,"역마진",IF(AH204&gt;=가정!$C$35,"GO",IF(AH204&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ204" s="7" t="n"/>
+      <c r="AK204" s="7" t="n"/>
+      <c r="AL204" s="6">
+        <f>IF(AK204="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK204,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="B205" s="6" t="n">
@@ -16386,7 +17588,7 @@
       </c>
       <c r="J205" s="10" t="n"/>
       <c r="K205" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L205" s="8" t="n"/>
@@ -16447,6 +17649,12 @@
         <f>IF(AH205="","",IF(U205&lt;=0,"역마진",IF(AH205&gt;=가정!$C$35,"GO",IF(AH205&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ205" s="7" t="n"/>
+      <c r="AK205" s="7" t="n"/>
+      <c r="AL205" s="6">
+        <f>IF(AK205="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK205,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="B206" s="6" t="n">
@@ -16465,7 +17673,7 @@
       </c>
       <c r="J206" s="10" t="n"/>
       <c r="K206" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L206" s="8" t="n"/>
@@ -16526,6 +17734,12 @@
         <f>IF(AH206="","",IF(U206&lt;=0,"역마진",IF(AH206&gt;=가정!$C$35,"GO",IF(AH206&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ206" s="7" t="n"/>
+      <c r="AK206" s="7" t="n"/>
+      <c r="AL206" s="6">
+        <f>IF(AK206="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK206,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="B207" s="6" t="n">
@@ -16544,7 +17758,7 @@
       </c>
       <c r="J207" s="10" t="n"/>
       <c r="K207" s="11">
-        <f>가정!$C$14</f>
+        <f>IF(가정!$C$38="로켓그로스",가정!$C$39,가정!$C$14)</f>
         <v/>
       </c>
       <c r="L207" s="8" t="n"/>
@@ -16605,6 +17819,12 @@
         <f>IF(AH207="","",IF(U207&lt;=0,"역마진",IF(AH207&gt;=가정!$C$35,"GO",IF(AH207&gt;=가정!$C$36,"검토","SKIP"))))</f>
         <v/>
       </c>
+      <c r="AJ207" s="7" t="n"/>
+      <c r="AK207" s="7" t="n"/>
+      <c r="AL207" s="6">
+        <f>IF(AK207="","",IFERROR(INDEX(로켓그로스요금표!$G$4:$G$9,MATCH(AK207,로켓그로스요금표!$B$4:$B$9,0)),"단계명 확인"))</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="B209" s="18" t="inlineStr">
@@ -16686,7 +17906,7 @@
         </is>
       </c>
       <c r="D216" s="9">
-        <f>가정!$C$38</f>
+        <f>가정!$C$45</f>
         <v/>
       </c>
     </row>
@@ -16697,7 +17917,7 @@
         </is>
       </c>
       <c r="D217" s="9">
-        <f>IFERROR(가정!$C$38/MAX(U8:U207),"")</f>
+        <f>IFERROR(가정!$C$45/MAX(U8:U207),"")</f>
         <v/>
       </c>
     </row>
@@ -16708,7 +17928,7 @@
         </is>
       </c>
       <c r="D218" s="20">
-        <f>IFERROR(가정!$C$38/MAX(U8:U207)/30,"")</f>
+        <f>IFERROR(가정!$C$45/MAX(U8:U207)/30,"")</f>
         <v/>
       </c>
     </row>
@@ -16947,7 +18167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D43"/>
+  <dimension ref="B2:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -17438,7 +18658,7 @@
     <row r="37">
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>⑥ 목표</t>
+          <t>⑥ 로켓그로스 (판매방식)</t>
         </is>
       </c>
       <c r="C37" s="22" t="n"/>
@@ -17447,56 +18667,159 @@
     <row r="38">
       <c r="B38" s="19" t="inlineStr">
         <is>
+          <t>기본 판매방식</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>로켓그로스</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>로켓그로스 / 마켓플레이스. 행별로 다르면 소싱현황 AJ열에서 덮어쓰기</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>로켓그로스 통합요율(K열)</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>판매수수료+입출고+배송+보관을 뭉뚱그린 실부담률. 검산: 수수료10.8%+출고2,500+입고500+보관300 ≈ 28.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>예상 재고 보관일수</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>쿠팡 센터 보관 예상일. 무료보관(30일, 의류·신발·악세 45일) 초과분에 보관료 부과</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>무료 보관일수</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>카테고리에 따라 30일 또는 45일</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>로켓그로스 세이버 구독</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Y면 월 99,000원으로 반품비·보관료 방어. 월 반품 20건↑ 또는 재고회전 30일↑이면 유리</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>세이버 월 구독료</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>99000</v>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>구독 시 월 고정비(판매수량으로 분산 판단)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>⑦ 목표</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="19" t="inlineStr">
+        <is>
           <t>월 목표 이익(원)</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C45" s="8" t="n">
         <v>500000</v>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D45" s="23" t="inlineStr">
         <is>
           <t>원본 V3의 '월 목표금액' 계승</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="25" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="25" t="inlineStr">
         <is>
           <t>색상 범례</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="26" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>직접 입력</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>노랑 = 여기를 채우세요</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="27" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>소싱 입력</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D49" s="23" t="inlineStr">
         <is>
           <t>연두 = 경쟁사 조사값 (소싱현황 AA~AE열)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="28" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>판정 결과</t>
         </is>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>주황 = 자동 판정 (소싱현황 AF~AI열)</t>
         </is>
@@ -17750,4 +19073,261 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>로켓그로스 입출고·보관 요금 (2025.1.6 개편 — 사이즈+무게 6단계)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>사이즈 단계</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>입고비</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>출고비</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>보관료(일)</t>
+        </is>
+      </c>
+      <c r="G3" s="29" t="inlineStr">
+        <is>
+          <t>물류비 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>초소형</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>20cm 이하 · 500g 미만</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>600</v>
+      </c>
+      <c r="F4" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="30">
+        <f>D4+E4+F4*MAX(0,가정!$C$40-가정!$C$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>소형</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>30cm 이하 · 1kg 미만</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" s="30">
+        <f>D5+E5+F5*MAX(0,가정!$C$40-가정!$C$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>중형</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>50cm 이하 · 3kg 미만</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="G6" s="30">
+        <f>D6+E6+F6*MAX(0,가정!$C$40-가정!$C$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>대형</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>60cm 이하 · 5kg 미만</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="30">
+        <f>D7+E7+F7*MAX(0,가정!$C$40-가정!$C$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>특대형</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>80cm 이하 · 10kg 미만</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>650</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="G8" s="30">
+        <f>D8+E8+F8*MAX(0,가정!$C$40-가정!$C$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>초대형</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>80cm 초과 또는 10kg 이상</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>800</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" s="30">
+        <f>D9+E9+F9*MAX(0,가정!$C$40-가정!$C$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>※ 입고비 100~800원 / 출고비 600~3,500원 / 보관료 일 10~50원 (공개 자료 기반 대표값 — 쿠팡 wing에서 실요율 확인 후 교정하세요).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>※ 무료보관: 일반 30일, 의류·신발·악세서리 45일. 초과분부터 보관료가 붙습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>※ 2025년부터 반품 회수·재입고 요금이 별도 부과됩니다(위 표에 미포함 — 보수적으로 여유를 두세요).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>※ 입출고비·배송비 프로모션은 2027.1.31까지 유효.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>※ 'G열 물류비 합계'를 소싱현황 L열(물류비)에 넣으면 정밀 계산이 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>※ 로켓그로스는 고객 택배비를 셀러가 부담하지 않습니다(쿠팡이 배송). 대신 출고비가 나갑니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/coupang-sourcing/excel/calc_v4_template.xlsx
+++ b/projects/coupang-sourcing/excel/calc_v4_template.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세율표" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="로켓그로스요금표" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수입실적" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="밀크런실적" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18716,7 +18717,7 @@
         </is>
       </c>
       <c r="D216" s="9">
-        <f>가정!$C$51</f>
+        <f>가정!$C$56</f>
         <v/>
       </c>
     </row>
@@ -18727,7 +18728,7 @@
         </is>
       </c>
       <c r="D217" s="9">
-        <f>IFERROR(가정!$C$51/MAX(U8:U207),"")</f>
+        <f>IFERROR(가정!$C$56/MAX(U8:U207),"")</f>
         <v/>
       </c>
     </row>
@@ -18738,7 +18739,7 @@
         </is>
       </c>
       <c r="D218" s="20">
-        <f>IFERROR(가정!$C$51/MAX(U8:U207)/30,"")</f>
+        <f>IFERROR(가정!$C$56/MAX(U8:U207)/30,"")</f>
         <v/>
       </c>
     </row>
@@ -18977,7 +18978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D56"/>
+  <dimension ref="B2:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -19665,7 +19666,7 @@
     <row r="50">
       <c r="B50" s="21" t="inlineStr">
         <is>
-          <t>⑦ 목표</t>
+          <t>⑦ 밀크런 (내 창고→쿠팡센터 입고)  ★정산 20건 실측</t>
         </is>
       </c>
       <c r="C50" s="22" t="n"/>
@@ -19674,56 +19675,125 @@
     <row r="51">
       <c r="B51" s="19" t="inlineStr">
         <is>
+          <t>밀크런 팔레트당 단가</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>29590</v>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>★실측: 26,900원(VAT별도) + 세액 2,690 = 29,590원. 3팔레트 건은 25,555원/팔레트로 소폭 할인</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>팔레트당 박스 수</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>★실측 평균 10.0개(249박스/25팔레트). 이 값이 클수록 개당 입고비 급감 — 6개면 4,932원/박스, 14개면 2,114원/박스로 2.3배 차이</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>박스당 상품 수</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>내 상품 기준 1박스에 몇 개 들어가는지</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>→ 개당 밀크런비</t>
+        </is>
+      </c>
+      <c r="C54" s="9">
+        <f>IFERROR($C$51/($C$52*$C$53),0)</f>
+        <v/>
+      </c>
+      <c r="D54" s="23">
+        <f> 팔레트당 단가 ÷ (팔레트당 박스수 × 박스당 상품수). L열(물류비)에 포함시킬 금액</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>⑧ 목표</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="19" t="inlineStr">
+        <is>
           <t>월 목표 이익(원)</t>
         </is>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C56" s="8" t="n">
         <v>500000</v>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D56" s="23" t="inlineStr">
         <is>
           <t>원본 V3의 '월 목표금액' 계승</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="25" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="25" t="inlineStr">
         <is>
           <t>색상 범례</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="26" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>직접 입력</t>
         </is>
       </c>
-      <c r="D54" s="23" t="inlineStr">
+      <c r="D59" s="23" t="inlineStr">
         <is>
           <t>노랑 = 여기를 채우세요</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="27" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>소싱 입력</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D60" s="23" t="inlineStr">
         <is>
           <t>연두 = 경쟁사 조사값 (소싱현황 AA~AE열)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="28" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="28" t="inlineStr">
         <is>
           <t>판정 결과</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D61" s="23" t="inlineStr">
         <is>
           <t>주황 = 자동 판정 (소싱현황 AF~AI열)</t>
         </is>
@@ -20664,4 +20734,802 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>밀크런 정산 실적 (내 창고 → 쿠팡 물류센터 입고 운송) 20건</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>픽업일</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>요금타입</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>팔레트</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>박스</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>발생금액</t>
+        </is>
+      </c>
+      <c r="G3" s="29" t="inlineStr">
+        <is>
+          <t>총액(VAT포함)</t>
+        </is>
+      </c>
+      <c r="H3" s="29" t="inlineStr">
+        <is>
+          <t>박스당</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>2026.03.11</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" s="30" t="n">
+        <v>53800</v>
+      </c>
+      <c r="G4" s="30" t="n">
+        <v>59180</v>
+      </c>
+      <c r="H4" s="36">
+        <f>IF(E4=0,"",G4/E4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>2026.03.11</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>취소금액</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>32500</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>35750</v>
+      </c>
+      <c r="H5" s="36">
+        <f>IF(E5=0,"",G5/E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>2026.03.12</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>53800</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>59180</v>
+      </c>
+      <c r="H6" s="36">
+        <f>IF(E6=0,"",G6/E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>2026.03.16</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>29590</v>
+      </c>
+      <c r="H7" s="36">
+        <f>IF(E7=0,"",G7/E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>2026.03.23</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>미청구</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="36">
+        <f>IF(E8=0,"",G8/E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>2026.03.23</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>29590</v>
+      </c>
+      <c r="H9" s="36">
+        <f>IF(E9=0,"",G9/E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>29590</v>
+      </c>
+      <c r="H10" s="36">
+        <f>IF(E10=0,"",G10/E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>29590</v>
+      </c>
+      <c r="H11" s="36">
+        <f>IF(E11=0,"",G11/E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.09</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>29590</v>
+      </c>
+      <c r="H12" s="36">
+        <f>IF(E12=0,"",G12/E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.09</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>29590</v>
+      </c>
+      <c r="H13" s="36">
+        <f>IF(E13=0,"",G13/E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.15</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>76665</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>84332</v>
+      </c>
+      <c r="H14" s="36">
+        <f>IF(E14=0,"",G14/E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>29590</v>
+      </c>
+      <c r="H15" s="36">
+        <f>IF(E15=0,"",G15/E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>29590</v>
+      </c>
+      <c r="H16" s="36">
+        <f>IF(E16=0,"",G16/E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>미청구</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="36">
+        <f>IF(E17=0,"",G17/E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.25</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>미청구</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="36">
+        <f>IF(E18=0,"",G18/E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.25</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>미청구</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="36">
+        <f>IF(E19=0,"",G19/E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.27</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>53800</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>59180</v>
+      </c>
+      <c r="H20" s="36">
+        <f>IF(E20=0,"",G20/E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.27</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>53800</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>59180</v>
+      </c>
+      <c r="H21" s="36">
+        <f>IF(E21=0,"",G21/E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.29</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="32" t="n">
+        <v>36</v>
+      </c>
+      <c r="F22" s="30" t="n">
+        <v>76665</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>84332</v>
+      </c>
+      <c r="H22" s="36">
+        <f>IF(E22=0,"",G22/E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>2026.04.29</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>밀크런이용</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>53800</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <v>59180</v>
+      </c>
+      <c r="H23" s="36">
+        <f>IF(E23=0,"",G23/E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>합계 (청구건만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>청구 건수</t>
+        </is>
+      </c>
+      <c r="D26" s="9">
+        <f>COUNTIFS(G4:G23,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>팔레트 합계</t>
+        </is>
+      </c>
+      <c r="D27" s="9">
+        <f>SUMIFS(D4:D23,G4:G23,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>박스 합계</t>
+        </is>
+      </c>
+      <c r="D28" s="9">
+        <f>SUMIFS(E4:E23,G4:G23,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>총액 합계</t>
+        </is>
+      </c>
+      <c r="D29" s="9">
+        <f>SUMIFS(G4:G23,G4:G23,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>→ 팔레트당 단가</t>
+        </is>
+      </c>
+      <c r="D30" s="9">
+        <f>IFERROR(D29/D27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>→ 박스당 단가</t>
+        </is>
+      </c>
+      <c r="D31" s="9">
+        <f>IFERROR(D29/D28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>→ 팔레트당 평균 박스</t>
+        </is>
+      </c>
+      <c r="D32" s="20">
+        <f>IFERROR(D28/D27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>핵심: 팔레트를 꽉 채울수록 개당 입고비가 급감합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  밀크런은 팔레트 단위 과금(26,900원/팔레트, VAT 포함 29,590원)이라 박스 수와 무관합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  실측 편차:  6박스/팔레트 → 4,932원/박스   vs   14박스/팔레트 → 2,114원/박스  (2.3배)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶ 입고 전에 팔레트 적재율을 최대로 올리는 것이 개당 원가를 낮추는 가장 쉬운 레버입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="23" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>전체 원가 사슬 (이 계산기가 반영하는 3개 구간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  중국 1688 ──[LCL 해상]──▶ 내 창고 ──[밀크런]──▶ 쿠팡센터 ──[로켓그로스]──▶ 고객</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     물품가×환율      고정 111,980 + 118,000/CBM    29,590/팔레트    입출고 1,375 + 배송 2,200~5,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="23" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>기타 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 미청구(무료) 4건 — 팔레트 7개·박스 65개분. 프로모션 또는 조건 충족 건으로 보입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 3팔레트 건은 76,665원 = 25,555원/팔레트로 소폭 할인(대량 인센티브 추정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 2026-03-11 '취소금액' 32,500원 1건 — 취소 수수료도 원가에 잡히니 주의.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/coupang-sourcing/excel/calc_v4_template.xlsx
+++ b/projects/coupang-sourcing/excel/calc_v4_template.xlsx
@@ -18717,7 +18717,7 @@
         </is>
       </c>
       <c r="D216" s="9">
-        <f>가정!$C$56</f>
+        <f>가정!$C$58</f>
         <v/>
       </c>
     </row>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="D217" s="9">
-        <f>IFERROR(가정!$C$56/MAX(U8:U207),"")</f>
+        <f>IFERROR(가정!$C$58/MAX(U8:U207),"")</f>
         <v/>
       </c>
     </row>
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="D218" s="20">
-        <f>IFERROR(가정!$C$56/MAX(U8:U207)/30,"")</f>
+        <f>IFERROR(가정!$C$58/MAX(U8:U207)/30,"")</f>
         <v/>
       </c>
     </row>
@@ -18978,7 +18978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D61"/>
+  <dimension ref="B2:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -19632,168 +19632,198 @@
     <row r="48">
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>신규 프로모션 적용중</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+          <t>개당 물류비(실측)</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>2551</v>
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>Y면 입출고비·배송비 0원(첫 판매 개시 후 90일간, 최대 90일 또는 누적매출 2억까지). 프로모션 중이면 K열 통합요율을 판매수수료만(약 11%)으로 낮추세요</t>
+          <t>★실측: 극소형 입출고 1,000 + 배송 1,551 = 2,551원(할인 후). 소형은 3,133원. 정액이므로 판매가가 낮을수록 부담률이 급등합니다</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>로켓그로스 세이버 적용</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
+          <t>로켓그로스 최소 권장가</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>★실측 근거: 이 아래면 물류비 비중이 17%를 넘어 통합 부담률이 30%를 초과합니다. 저가 상품은 묶음 구성으로 객단가를 올리거나 마켓플레이스로 전환하세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>신규 프로모션 적용중</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
-        <is>
-          <t>Y면 보관 60일까지 무료 + 반품 회수·재입고 무제한 무료. 90일 이후에도 270일간 0원 프로모션 중</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>⑦ 밀크런 (내 창고→쿠팡센터 입고)  ★정산 20건 실측</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>Y면 입출고비·배송비 0원(첫 판매 개시 후 90일간, 최대 90일 또는 누적매출 2억까지). 프로모션 중이면 K열 통합요율을 판매수수료만(약 11%)으로 낮추세요</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>밀크런 팔레트당 단가</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="n">
-        <v>29590</v>
+          <t>로켓그로스 세이버 적용</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>★실측: 26,900원(VAT별도) + 세액 2,690 = 29,590원. 3팔레트 건은 25,555원/팔레트로 소폭 할인</t>
+          <t>Y면 보관 60일까지 무료 + 반품 회수·재입고 무제한 무료. 90일 이후에도 270일간 0원 프로모션 중</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>팔레트당 박스 수</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D52" s="23" t="inlineStr">
-        <is>
-          <t>★실측 평균 10.0개(249박스/25팔레트). 이 값이 클수록 개당 입고비 급감 — 6개면 4,932원/박스, 14개면 2,114원/박스로 2.3배 차이</t>
-        </is>
-      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>⑦ 밀크런 (내 창고→쿠팡센터 입고)  ★정산 20건 실측</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t>박스당 상품 수</t>
+          <t>밀크런 팔레트당 단가</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>20</v>
+        <v>29590</v>
       </c>
       <c r="D53" s="23" t="inlineStr">
         <is>
-          <t>내 상품 기준 1박스에 몇 개 들어가는지</t>
+          <t>★실측: 26,900원(VAT별도) + 세액 2,690 = 29,590원. 3팔레트 건은 25,555원/팔레트로 소폭 할인</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>→ 개당 밀크런비</t>
-        </is>
-      </c>
-      <c r="C54" s="9">
-        <f>IFERROR($C$51/($C$52*$C$53),0)</f>
-        <v/>
-      </c>
-      <c r="D54" s="23">
-        <f> 팔레트당 단가 ÷ (팔레트당 박스수 × 박스당 상품수). L열(물류비)에 포함시킬 금액</f>
-        <v/>
+          <t>팔레트당 박스 수</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>★실측 평균 10.0개(249박스/25팔레트). 이 값이 클수록 개당 입고비 급감 — 6개면 4,932원/박스, 14개면 2,114원/박스로 2.3배 차이</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="21" t="inlineStr">
-        <is>
-          <t>⑧ 목표</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="22" t="n"/>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>박스당 상품 수</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>내 상품 기준 1박스에 몇 개 들어가는지</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="B56" s="19" t="inlineStr">
         <is>
+          <t>→ 개당 밀크런비</t>
+        </is>
+      </c>
+      <c r="C56" s="9">
+        <f>IFERROR($C$53/($C$54*$C$55),0)</f>
+        <v/>
+      </c>
+      <c r="D56" s="23">
+        <f> 팔레트당 단가 ÷ (팔레트당 박스수 × 박스당 상품수). L열(물류비)에 포함시킬 금액</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>⑧ 목표</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="22" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="19" t="inlineStr">
+        <is>
           <t>월 목표 이익(원)</t>
         </is>
       </c>
-      <c r="C56" s="8" t="n">
+      <c r="C58" s="8" t="n">
         <v>500000</v>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D58" s="23" t="inlineStr">
         <is>
           <t>원본 V3의 '월 목표금액' 계승</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="25" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="25" t="inlineStr">
         <is>
           <t>색상 범례</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="26" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>직접 입력</t>
         </is>
       </c>
-      <c r="D59" s="23" t="inlineStr">
+      <c r="D61" s="23" t="inlineStr">
         <is>
           <t>노랑 = 여기를 채우세요</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="27" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>소싱 입력</t>
         </is>
       </c>
-      <c r="D60" s="23" t="inlineStr">
+      <c r="D62" s="23" t="inlineStr">
         <is>
           <t>연두 = 경쟁사 조사값 (소싱현황 AA~AE열)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="28" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="28" t="inlineStr">
         <is>
           <t>판정 결과</t>
         </is>
       </c>
-      <c r="D61" s="23" t="inlineStr">
+      <c r="D63" s="23" t="inlineStr">
         <is>
           <t>주황 = 자동 판정 (소싱현황 AF~AI열)</t>
         </is>
@@ -20055,7 +20085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G24"/>
+  <dimension ref="B2:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -20070,19 +20100,19 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>로켓그로스 비용 구성 — 쿠팡 공식 고지값</t>
+          <t>로켓그로스 물류비 — CFS 정산 27,318개 실측 (할인 적용 후)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>사이즈 유형</t>
+          <t>사이즈</t>
         </is>
       </c>
       <c r="C3" s="29" t="inlineStr">
         <is>
-          <t>예시</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="D3" s="29" t="inlineStr">
@@ -20102,85 +20132,85 @@
       </c>
       <c r="G3" s="29" t="inlineStr">
         <is>
-          <t>실적용 물류비</t>
+          <t>개당 물류비</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>Large Size 1</t>
+          <t>극소형</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>전자레인지 크기</t>
+          <t>실측 25,031개 (전체의 92%)</t>
         </is>
       </c>
       <c r="D4" s="30" t="n">
-        <v>1375</v>
+        <v>1000</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>2200</v>
+        <v>1551</v>
       </c>
       <c r="F4" s="32">
-        <f>가정!$C$48</f>
+        <f>가정!$C$50</f>
         <v/>
       </c>
       <c r="G4" s="30">
-        <f>IF(가정!$C$48="Y",0,D4+E4)</f>
+        <f>IF(가정!$C$50="Y",0,D4+E4)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>Large Size 2</t>
+          <t>소형</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>의자 크기</t>
+          <t>실측 2,291개</t>
         </is>
       </c>
       <c r="D5" s="30" t="n">
-        <v>1375</v>
+        <v>1149</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>4100</v>
+        <v>1984</v>
       </c>
       <c r="F5" s="32">
-        <f>가정!$C$48</f>
+        <f>가정!$C$50</f>
         <v/>
       </c>
       <c r="G5" s="30">
-        <f>IF(가정!$C$48="Y",0,D5+E5)</f>
+        <f>IF(가정!$C$50="Y",0,D5+E5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>Extra Large Size</t>
+          <t>(참고)공식고지</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>서랍장 크기</t>
+          <t>할인 전 정가 — Large Size 1</t>
         </is>
       </c>
       <c r="D6" s="30" t="n">
         <v>1375</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>5600</v>
+        <v>2200</v>
       </c>
       <c r="F6" s="32">
-        <f>가정!$C$48</f>
+        <f>가정!$C$50</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(가정!$C$48="Y",0,D6+E6)</f>
+        <f>IF(가정!$C$50="Y",0,D6+E6)</f>
         <v/>
       </c>
     </row>
@@ -20302,68 +20332,373 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>※ 판매수수료는 '판매자배송과 동일'(카테고리별). 위 입출고비·배송비는 판매된 상품에만 부과됩니다.</t>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>★ 판매가별 통합 부담률 (판매수수료 10.86% + 물류비 정액 2,551원)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>※ 프로모션: 첫 판매 개시 후 90일간 로켓그로스 시작비용 0원 — 최대 90일 또는 누적매출 2억원 달성 시까지.</t>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>물류비</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>물류비 비중</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>수수료</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>통합 부담률</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>30% 가정 대비</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>※ 로켓그로스 세이버: 90일 이후에도 270일간 0원 프로모션(보관 60일 미경과 상품 대상).</t>
-        </is>
+      <c r="B17" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C17" s="30">
+        <f>$D$4+$E$4</f>
+        <v/>
+      </c>
+      <c r="D17" s="31">
+        <f>C17/B17</f>
+        <v/>
+      </c>
+      <c r="E17" s="31">
+        <f>가정!$C$18*1.1</f>
+        <v/>
+      </c>
+      <c r="F17" s="31">
+        <f>D17+E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="31">
+        <f>F17-가정!$C$45</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>※ 프로모션 신청기간 2026.07.01~07.31 · 대상: 기간 내 판매 개시한 로켓그로스 신규 판매자.</t>
-        </is>
+      <c r="B18" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C18" s="30">
+        <f>$D$4+$E$4</f>
+        <v/>
+      </c>
+      <c r="D18" s="31">
+        <f>C18/B18</f>
+        <v/>
+      </c>
+      <c r="E18" s="31">
+        <f>가정!$C$18*1.1</f>
+        <v/>
+      </c>
+      <c r="F18" s="31">
+        <f>D18+E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="31">
+        <f>F18-가정!$C$45</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>※ 부가서비스: 반출 배송 90일 무료(최대 10만원), 바코드 부착·오류수정은 별도.</t>
-        </is>
+      <c r="B19" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C19" s="30">
+        <f>$D$4+$E$4</f>
+        <v/>
+      </c>
+      <c r="D19" s="31">
+        <f>C19/B19</f>
+        <v/>
+      </c>
+      <c r="E19" s="31">
+        <f>가정!$C$18*1.1</f>
+        <v/>
+      </c>
+      <c r="F19" s="31">
+        <f>D19+E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="31">
+        <f>F19-가정!$C$45</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>※ 카테고리·사이즈유형·판매가에 따라 최종 비용이 결정되므로, wing의 '입출고/배송 비용 확인하기'로 상품별 실요율을 확인하세요.</t>
-        </is>
+      <c r="B20" s="30" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C20" s="30">
+        <f>$D$4+$E$4</f>
+        <v/>
+      </c>
+      <c r="D20" s="31">
+        <f>C20/B20</f>
+        <v/>
+      </c>
+      <c r="E20" s="31">
+        <f>가정!$C$18*1.1</f>
+        <v/>
+      </c>
+      <c r="F20" s="31">
+        <f>D20+E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="31">
+        <f>F20-가정!$C$45</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="inlineStr"/>
+      <c r="B21" s="30" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C21" s="30">
+        <f>$D$4+$E$4</f>
+        <v/>
+      </c>
+      <c r="D21" s="31">
+        <f>C21/B21</f>
+        <v/>
+      </c>
+      <c r="E21" s="31">
+        <f>가정!$C$18*1.1</f>
+        <v/>
+      </c>
+      <c r="F21" s="31">
+        <f>D21+E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="31">
+        <f>F21-가정!$C$45</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>▶ 검산: 판매가 20,000원 · Large Size 1 기준</t>
-        </is>
+      <c r="B22" s="30" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C22" s="30">
+        <f>$D$4+$E$4</f>
+        <v/>
+      </c>
+      <c r="D22" s="31">
+        <f>C22/B22</f>
+        <v/>
+      </c>
+      <c r="E22" s="31">
+        <f>가정!$C$18*1.1</f>
+        <v/>
+      </c>
+      <c r="F22" s="31">
+        <f>D22+E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="31">
+        <f>F22-가정!$C$45</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   판매수수료 10.86%(2,172) + 입출고비 1,375 + 배송비 2,200 = 5,747원 = 판매가의 28.7%</t>
-        </is>
+      <c r="B23" s="30" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C23" s="30">
+        <f>$D$4+$E$4</f>
+        <v/>
+      </c>
+      <c r="D23" s="31">
+        <f>C23/B23</f>
+        <v/>
+      </c>
+      <c r="E23" s="31">
+        <f>가정!$C$18*1.1</f>
+        <v/>
+      </c>
+      <c r="F23" s="31">
+        <f>D23+E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="31">
+        <f>F23-가정!$C$45</f>
+        <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → 소싱현황 K열의 통합요율 30% 가정이 실제와 부합합니다(프로모션 종료 후 기준).</t>
+      <c r="B24" s="30" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C24" s="30">
+        <f>$D$4+$E$4</f>
+        <v/>
+      </c>
+      <c r="D24" s="31">
+        <f>C24/B24</f>
+        <v/>
+      </c>
+      <c r="E24" s="31">
+        <f>가정!$C$18*1.1</f>
+        <v/>
+      </c>
+      <c r="F24" s="31">
+        <f>D24+E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="31">
+        <f>F24-가정!$C$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>★ 30% 고정 가정의 한계 — 실측으로 드러난 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  물류비는 개당 정액(극소형 2,551원)이라 판매가가 낮을수록 부담률이 폭증합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  실측 상품별 통합 부담률:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     브라끈 4,990원      → 61.6%  (30% 가정 대비 +31.6%p)  ⚠️ 심각한 과소평가</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     이불보관함 8,600원   → 49.8%  (+19.8%p)  ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     압축파우치 10,520원  → 35.4%  (+5.4%p)   ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     꼬마정원등 14,300원  → 28.7%  (−1.3%p)   ✅ 30% 가정이 맞는 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     계단등 16,700원     → 25.3%  (−4.7%p)   💰 여유</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     문주등 56,000원     → 14.2%  (−15.8%p)  💰 매우 여유</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>▶ 결론: 로켓그로스는 판매가 1.5만원 이상에서 유리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1만원 이하 저가 상품은 물류비만 판매가의 25~50%를 먹어 마진이 남지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   저가 상품은 ①묶음 구성으로 객단가를 올리거나 ②마켓플레이스(셀러배송)로 전환하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="23" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>그 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 위 입출고비·배송비는 할인 적용 후 실제 청구액입니다(정가 대비 입출고 −39%, 배송 −12%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 판매수수료는 '판매자배송과 동일'(카테고리별). 판매된 상품에만 부과됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 프로모션: 첫 판매 개시 후 90일간 입출고비·배송비 0원(최대 90일 또는 누적매출 2억까지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 로켓세이버: 90일 이후에도 270일간 0원(보관 60일 미경과 상품). 반품 회수·재입고 무제한 무료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 상품별 실요율은 wing의 '입출고/배송 비용 확인하기'에서 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -20371,6 +20706,11 @@
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="G17:G24">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0.03</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
